--- a/data/Patient List June 2026.xlsx
+++ b/data/Patient List June 2026.xlsx
@@ -446,17 +446,17 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S9"/>
+  <dimension ref="A1:S128"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
     <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="17" customWidth="1" min="3" max="3"/>
+    <col width="23" customWidth="1" min="3" max="3"/>
     <col width="7" customWidth="1" min="4" max="4"/>
     <col width="14" customWidth="1" min="5" max="5"/>
     <col width="9" customWidth="1" min="6" max="6"/>
-    <col width="19" customWidth="1" min="7" max="7"/>
-    <col width="17" customWidth="1" min="8" max="8"/>
+    <col width="22" customWidth="1" min="7" max="7"/>
+    <col width="26" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
     <col width="21" customWidth="1" min="10" max="10"/>
     <col width="28" customWidth="1" min="11" max="11"/>
@@ -579,7 +579,7 @@
     </row>
     <row r="6">
       <c r="A6" s="5" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
@@ -588,12 +588,12 @@
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>Arshad</t>
+          <t>Naseem Akhtar</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>50y</t>
+          <t>63y</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
@@ -603,7 +603,7 @@
       </c>
       <c r="G6" s="5" t="inlineStr">
         <is>
-          <t>Dr. Anjum Rana</t>
+          <t>Dr. Suleman Khan</t>
         </is>
       </c>
       <c r="H6" s="5" t="inlineStr">
@@ -637,12 +637,12 @@
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>Faiz Muhammad</t>
+          <t>Ijaz Anwar</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>50y</t>
+          <t>40y</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
@@ -652,26 +652,26 @@
       </c>
       <c r="G7" s="5" t="inlineStr">
         <is>
-          <t>Dr. Anjum Rana</t>
+          <t>Dr. Ali Hameed</t>
         </is>
       </c>
       <c r="H7" s="5" t="inlineStr">
         <is>
-          <t>C/Angio + PCI</t>
+          <t>C/Angio</t>
         </is>
       </c>
       <c r="I7" s="5" t="n">
-        <v>22908</v>
+        <v>35000</v>
       </c>
       <c r="J7" s="5" t="n">
-        <v>17519</v>
+        <v>1369</v>
       </c>
       <c r="K7" s="5" t="n">
-        <v>5389</v>
+        <v>33631</v>
       </c>
       <c r="N7" s="5" t="inlineStr">
         <is>
-          <t>11500</t>
+          <t>11750</t>
         </is>
       </c>
     </row>
@@ -681,17 +681,17 @@
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>02/06/2026</t>
+          <t>01/06/2026</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>Arshad</t>
+          <t>Razia Perveen</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>50y</t>
+          <t>56y</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
@@ -701,7 +701,7 @@
       </c>
       <c r="G8" s="5" t="inlineStr">
         <is>
-          <t>Dr. Anjum Rana</t>
+          <t>Dr. Ali Hameed</t>
         </is>
       </c>
       <c r="H8" s="5" t="inlineStr">
@@ -720,7 +720,7 @@
       </c>
       <c r="N8" s="5" t="inlineStr">
         <is>
-          <t>11500</t>
+          <t>11750</t>
         </is>
       </c>
     </row>
@@ -730,17 +730,17 @@
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>05/06/2026</t>
+          <t>01/06/2026</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>Ahmed</t>
+          <t>M. Tahir Munir</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>50y</t>
+          <t>61y</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
@@ -750,26 +750,5857 @@
       </c>
       <c r="G9" s="5" t="inlineStr">
         <is>
-          <t>Dr. Anjum Rana</t>
+          <t>Dr. Kashif Zaffar</t>
         </is>
       </c>
       <c r="H9" s="5" t="inlineStr">
         <is>
-          <t>C/Angio + PCI</t>
+          <t>C/Angio</t>
         </is>
       </c>
       <c r="I9" s="5" t="n">
         <v>22908</v>
       </c>
       <c r="J9" s="5" t="n">
+        <v>1369</v>
+      </c>
+      <c r="K9" s="5" t="n">
+        <v>21539</v>
+      </c>
+      <c r="N9" s="5" t="inlineStr">
+        <is>
+          <t>16500</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="B10" s="5" t="inlineStr">
+        <is>
+          <t>01/06/2026</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>M. Safdar</t>
+        </is>
+      </c>
+      <c r="D10" s="5" t="inlineStr">
+        <is>
+          <t>50y</t>
+        </is>
+      </c>
+      <c r="E10" s="5" t="inlineStr">
+        <is>
+          <t>Healthcard</t>
+        </is>
+      </c>
+      <c r="G10" s="5" t="inlineStr">
+        <is>
+          <t>Dr. Suleman Khan</t>
+        </is>
+      </c>
+      <c r="H10" s="5" t="inlineStr">
+        <is>
+          <t>C/Angio</t>
+        </is>
+      </c>
+      <c r="I10" s="5" t="n">
+        <v>22908</v>
+      </c>
+      <c r="J10" s="5" t="n">
+        <v>1369</v>
+      </c>
+      <c r="K10" s="5" t="n">
+        <v>21539</v>
+      </c>
+      <c r="N10" s="5" t="inlineStr">
+        <is>
+          <t>11500</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="B11" s="5" t="inlineStr">
+        <is>
+          <t>01/06/2026</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>M. Sarfraz</t>
+        </is>
+      </c>
+      <c r="D11" s="5" t="inlineStr">
+        <is>
+          <t>58y</t>
+        </is>
+      </c>
+      <c r="E11" s="5" t="inlineStr">
+        <is>
+          <t>Healthcard</t>
+        </is>
+      </c>
+      <c r="G11" s="5" t="inlineStr">
+        <is>
+          <t>Dr. M. Ijaz</t>
+        </is>
+      </c>
+      <c r="H11" s="5" t="inlineStr">
+        <is>
+          <t>C/Angio + PCI</t>
+        </is>
+      </c>
+      <c r="I11" s="5" t="n">
+        <v>194718</v>
+      </c>
+      <c r="J11" s="5" t="n">
+        <v>11650</v>
+      </c>
+      <c r="K11" s="5" t="n">
+        <v>183068</v>
+      </c>
+      <c r="N11" s="5" t="inlineStr">
+        <is>
+          <t>91000</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="B12" s="5" t="inlineStr">
+        <is>
+          <t>01/06/2026</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="inlineStr">
+        <is>
+          <t>Khalid Latif</t>
+        </is>
+      </c>
+      <c r="D12" s="5" t="inlineStr">
+        <is>
+          <t>69y</t>
+        </is>
+      </c>
+      <c r="E12" s="5" t="inlineStr">
+        <is>
+          <t>Healthcard</t>
+        </is>
+      </c>
+      <c r="G12" s="5" t="inlineStr">
+        <is>
+          <t>Dr. Anjum Rana</t>
+        </is>
+      </c>
+      <c r="H12" s="5" t="inlineStr">
+        <is>
+          <t>C/Angio + PCI</t>
+        </is>
+      </c>
+      <c r="I12" s="5" t="n">
+        <v>400000</v>
+      </c>
+      <c r="J12" s="5" t="n">
+        <v>11650</v>
+      </c>
+      <c r="K12" s="5" t="n">
+        <v>388350</v>
+      </c>
+      <c r="N12" s="5" t="inlineStr">
+        <is>
+          <t>46500</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="B13" s="5" t="inlineStr">
+        <is>
+          <t>01/06/2026</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="inlineStr">
+        <is>
+          <t>Iftikhar Ahmed</t>
+        </is>
+      </c>
+      <c r="D13" s="5" t="inlineStr">
+        <is>
+          <t>50y</t>
+        </is>
+      </c>
+      <c r="E13" s="5" t="inlineStr">
+        <is>
+          <t>Healthcard</t>
+        </is>
+      </c>
+      <c r="G13" s="5" t="inlineStr">
+        <is>
+          <t>Dr. Anjum Rana</t>
+        </is>
+      </c>
+      <c r="H13" s="5" t="inlineStr">
+        <is>
+          <t>C/Angio + PCI</t>
+        </is>
+      </c>
+      <c r="I13" s="5" t="n">
+        <v>370000</v>
+      </c>
+      <c r="J13" s="5" t="n">
+        <v>11650</v>
+      </c>
+      <c r="K13" s="5" t="n">
+        <v>358350</v>
+      </c>
+      <c r="N13" s="5" t="inlineStr">
+        <is>
+          <t>82500</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="5" t="n">
+        <v>9</v>
+      </c>
+      <c r="B14" s="5" t="inlineStr">
+        <is>
+          <t>01/06/2026</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="inlineStr">
+        <is>
+          <t>Nafees Ahmed</t>
+        </is>
+      </c>
+      <c r="D14" s="5" t="inlineStr">
+        <is>
+          <t>58y</t>
+        </is>
+      </c>
+      <c r="E14" s="5" t="inlineStr">
+        <is>
+          <t>Healthcard</t>
+        </is>
+      </c>
+      <c r="G14" s="5" t="inlineStr">
+        <is>
+          <t>Dr. Anjum Rana</t>
+        </is>
+      </c>
+      <c r="H14" s="5" t="inlineStr">
+        <is>
+          <t>C/Angio + PCI</t>
+        </is>
+      </c>
+      <c r="I14" s="5" t="n">
+        <v>286350</v>
+      </c>
+      <c r="J14" s="5" t="n">
+        <v>17519</v>
+      </c>
+      <c r="K14" s="5" t="n">
+        <v>268831</v>
+      </c>
+      <c r="N14" s="5" t="inlineStr">
+        <is>
+          <t>124500</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="B15" s="5" t="inlineStr">
+        <is>
+          <t>02/06/2026</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="inlineStr">
+        <is>
+          <t>Waris Ali</t>
+        </is>
+      </c>
+      <c r="D15" s="5" t="inlineStr">
+        <is>
+          <t>46y</t>
+        </is>
+      </c>
+      <c r="E15" s="5" t="inlineStr">
+        <is>
+          <t>Healthcard</t>
+        </is>
+      </c>
+      <c r="G15" s="5" t="inlineStr">
+        <is>
+          <t>Dr. Anjum Rana</t>
+        </is>
+      </c>
+      <c r="H15" s="5" t="inlineStr">
+        <is>
+          <t>C/Angio</t>
+        </is>
+      </c>
+      <c r="I15" s="5" t="n">
+        <v>22908</v>
+      </c>
+      <c r="J15" s="5" t="n">
+        <v>1369</v>
+      </c>
+      <c r="K15" s="5" t="n">
+        <v>21539</v>
+      </c>
+      <c r="N15" s="5" t="inlineStr">
+        <is>
+          <t>11500</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="5" t="n">
+        <v>11</v>
+      </c>
+      <c r="B16" s="5" t="inlineStr">
+        <is>
+          <t>02/06/2026</t>
+        </is>
+      </c>
+      <c r="C16" s="5" t="inlineStr">
+        <is>
+          <t>Shaista Perveen</t>
+        </is>
+      </c>
+      <c r="D16" s="5" t="inlineStr">
+        <is>
+          <t>60y</t>
+        </is>
+      </c>
+      <c r="E16" s="5" t="inlineStr">
+        <is>
+          <t>Healthcard</t>
+        </is>
+      </c>
+      <c r="G16" s="5" t="inlineStr">
+        <is>
+          <t>Dr. Suleman Khan</t>
+        </is>
+      </c>
+      <c r="H16" s="5" t="inlineStr">
+        <is>
+          <t>C/Angio</t>
+        </is>
+      </c>
+      <c r="I16" s="5" t="n">
+        <v>22908</v>
+      </c>
+      <c r="J16" s="5" t="n">
+        <v>1369</v>
+      </c>
+      <c r="K16" s="5" t="n">
+        <v>21539</v>
+      </c>
+      <c r="N16" s="5" t="inlineStr">
+        <is>
+          <t>9000</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="5" t="n">
+        <v>12</v>
+      </c>
+      <c r="B17" s="5" t="inlineStr">
+        <is>
+          <t>02/06/2026</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="inlineStr">
+        <is>
+          <t>Wahid Ali</t>
+        </is>
+      </c>
+      <c r="D17" s="5" t="inlineStr">
+        <is>
+          <t>47y</t>
+        </is>
+      </c>
+      <c r="E17" s="5" t="inlineStr">
+        <is>
+          <t>Healthcard</t>
+        </is>
+      </c>
+      <c r="G17" s="5" t="inlineStr">
+        <is>
+          <t>Dr. Ali Hameed</t>
+        </is>
+      </c>
+      <c r="H17" s="5" t="inlineStr">
+        <is>
+          <t>C/Angio + PCI</t>
+        </is>
+      </c>
+      <c r="I17" s="5" t="n">
+        <v>194718</v>
+      </c>
+      <c r="J17" s="5" t="n">
+        <v>11650</v>
+      </c>
+      <c r="K17" s="5" t="n">
+        <v>183068</v>
+      </c>
+      <c r="N17" s="5" t="inlineStr">
+        <is>
+          <t>105250</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="5" t="n">
+        <v>13</v>
+      </c>
+      <c r="B18" s="5" t="inlineStr">
+        <is>
+          <t>02/06/2026</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="inlineStr">
+        <is>
+          <t>Zubaida</t>
+        </is>
+      </c>
+      <c r="D18" s="5" t="inlineStr">
+        <is>
+          <t>50y</t>
+        </is>
+      </c>
+      <c r="E18" s="5" t="inlineStr">
+        <is>
+          <t>Healthcard</t>
+        </is>
+      </c>
+      <c r="G18" s="5" t="inlineStr">
+        <is>
+          <t>Dr. Imran Abid</t>
+        </is>
+      </c>
+      <c r="H18" s="5" t="inlineStr">
+        <is>
+          <t>C/Angio + PCI</t>
+        </is>
+      </c>
+      <c r="I18" s="5" t="n">
+        <v>286350</v>
+      </c>
+      <c r="J18" s="5" t="n">
+        <v>17519</v>
+      </c>
+      <c r="K18" s="5" t="n">
+        <v>268831</v>
+      </c>
+      <c r="N18" s="5" t="inlineStr">
+        <is>
+          <t>136500</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="5" t="n">
+        <v>14</v>
+      </c>
+      <c r="B19" s="5" t="inlineStr">
+        <is>
+          <t>02/06/2026</t>
+        </is>
+      </c>
+      <c r="C19" s="5" t="inlineStr">
+        <is>
+          <t>Razia</t>
+        </is>
+      </c>
+      <c r="D19" s="5" t="inlineStr">
+        <is>
+          <t>56y</t>
+        </is>
+      </c>
+      <c r="E19" s="5" t="inlineStr">
+        <is>
+          <t>Healthcard</t>
+        </is>
+      </c>
+      <c r="G19" s="5" t="inlineStr">
+        <is>
+          <t>Dr. Suleman Khan</t>
+        </is>
+      </c>
+      <c r="H19" s="5" t="inlineStr">
+        <is>
+          <t>C/Angio + PCI</t>
+        </is>
+      </c>
+      <c r="I19" s="5" t="n">
+        <v>173802</v>
+      </c>
+      <c r="J19" s="5" t="n">
+        <v>17519</v>
+      </c>
+      <c r="K19" s="5" t="n">
+        <v>156283</v>
+      </c>
+      <c r="N19" s="5" t="inlineStr">
+        <is>
+          <t>133100</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="5" t="n">
+        <v>15</v>
+      </c>
+      <c r="B20" s="5" t="inlineStr">
+        <is>
+          <t>02/06/2026</t>
+        </is>
+      </c>
+      <c r="C20" s="5" t="inlineStr">
+        <is>
+          <t>M. Ashfaq</t>
+        </is>
+      </c>
+      <c r="D20" s="5" t="inlineStr">
+        <is>
+          <t>62y</t>
+        </is>
+      </c>
+      <c r="E20" s="5" t="inlineStr">
+        <is>
+          <t>Healthcard</t>
+        </is>
+      </c>
+      <c r="G20" s="5" t="inlineStr">
+        <is>
+          <t>Dr. Anjum Rana</t>
+        </is>
+      </c>
+      <c r="H20" s="5" t="inlineStr">
+        <is>
+          <t>C/Angio + PCI + Plasty</t>
+        </is>
+      </c>
+      <c r="I20" s="5" t="n">
+        <v>343620</v>
+      </c>
+      <c r="J20" s="5" t="n">
         <v>20542</v>
       </c>
-      <c r="K9" s="5" t="n">
-        <v>2366</v>
-      </c>
-      <c r="N9" s="5" t="inlineStr">
+      <c r="K20" s="5" t="n">
+        <v>323078</v>
+      </c>
+      <c r="N20" s="5" t="inlineStr">
+        <is>
+          <t>182500</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="5" t="n">
+        <v>16</v>
+      </c>
+      <c r="B21" s="5" t="inlineStr">
+        <is>
+          <t>03/06/2026</t>
+        </is>
+      </c>
+      <c r="C21" s="5" t="inlineStr">
+        <is>
+          <t>Shah Muhammad</t>
+        </is>
+      </c>
+      <c r="D21" s="5" t="inlineStr">
+        <is>
+          <t>69y</t>
+        </is>
+      </c>
+      <c r="E21" s="5" t="inlineStr">
+        <is>
+          <t>Healthcard</t>
+        </is>
+      </c>
+      <c r="G21" s="5" t="inlineStr">
+        <is>
+          <t>Dr. Matti-ullah</t>
+        </is>
+      </c>
+      <c r="H21" s="5" t="inlineStr">
+        <is>
+          <t>C/Angio</t>
+        </is>
+      </c>
+      <c r="I21" s="5" t="n">
+        <v>22908</v>
+      </c>
+      <c r="J21" s="5" t="n">
+        <v>1369</v>
+      </c>
+      <c r="K21" s="5" t="n">
+        <v>21539</v>
+      </c>
+      <c r="N21" s="5" t="inlineStr">
+        <is>
+          <t>11750</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="5" t="n">
+        <v>17</v>
+      </c>
+      <c r="B22" s="5" t="inlineStr">
+        <is>
+          <t>03/06/2026</t>
+        </is>
+      </c>
+      <c r="C22" s="5" t="inlineStr">
+        <is>
+          <t>M. Shafique</t>
+        </is>
+      </c>
+      <c r="D22" s="5" t="inlineStr">
+        <is>
+          <t>50y</t>
+        </is>
+      </c>
+      <c r="E22" s="5" t="inlineStr">
+        <is>
+          <t>Healthcard</t>
+        </is>
+      </c>
+      <c r="G22" s="5" t="inlineStr">
+        <is>
+          <t>Dr. Suleman Khan</t>
+        </is>
+      </c>
+      <c r="H22" s="5" t="inlineStr">
+        <is>
+          <t>C/Angio</t>
+        </is>
+      </c>
+      <c r="I22" s="5" t="n">
+        <v>22908</v>
+      </c>
+      <c r="J22" s="5" t="n">
+        <v>1369</v>
+      </c>
+      <c r="K22" s="5" t="n">
+        <v>21539</v>
+      </c>
+      <c r="N22" s="5" t="inlineStr">
         <is>
           <t>11500</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="5" t="n">
+        <v>18</v>
+      </c>
+      <c r="B23" s="5" t="inlineStr">
+        <is>
+          <t>03/06/2026</t>
+        </is>
+      </c>
+      <c r="C23" s="5" t="inlineStr">
+        <is>
+          <t>M. Mubarak</t>
+        </is>
+      </c>
+      <c r="D23" s="5" t="inlineStr">
+        <is>
+          <t>50y</t>
+        </is>
+      </c>
+      <c r="E23" s="5" t="inlineStr">
+        <is>
+          <t>Healthcard</t>
+        </is>
+      </c>
+      <c r="G23" s="5" t="inlineStr">
+        <is>
+          <t>Dr. Suleman Khan</t>
+        </is>
+      </c>
+      <c r="H23" s="5" t="inlineStr">
+        <is>
+          <t>C/Angio + PCI</t>
+        </is>
+      </c>
+      <c r="I23" s="5" t="n">
+        <v>286350</v>
+      </c>
+      <c r="J23" s="5" t="n">
+        <v>17519</v>
+      </c>
+      <c r="K23" s="5" t="n">
+        <v>268831</v>
+      </c>
+      <c r="N23" s="5" t="inlineStr">
+        <is>
+          <t>134500</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="5" t="n">
+        <v>19</v>
+      </c>
+      <c r="B24" s="5" t="inlineStr">
+        <is>
+          <t>04/06/2026</t>
+        </is>
+      </c>
+      <c r="C24" s="5" t="inlineStr">
+        <is>
+          <t>Rizwana Waris</t>
+        </is>
+      </c>
+      <c r="D24" s="5" t="inlineStr">
+        <is>
+          <t>50y</t>
+        </is>
+      </c>
+      <c r="E24" s="5" t="inlineStr">
+        <is>
+          <t>Healthcard</t>
+        </is>
+      </c>
+      <c r="G24" s="5" t="inlineStr">
+        <is>
+          <t>Dr. Anjum Rana</t>
+        </is>
+      </c>
+      <c r="H24" s="5" t="inlineStr">
+        <is>
+          <t>C/Angio</t>
+        </is>
+      </c>
+      <c r="I24" s="5" t="n">
+        <v>25000</v>
+      </c>
+      <c r="J24" s="5" t="n">
+        <v>1369</v>
+      </c>
+      <c r="K24" s="5" t="n">
+        <v>23631</v>
+      </c>
+      <c r="N24" s="5" t="inlineStr">
+        <is>
+          <t>11500</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="5" t="n">
+        <v>20</v>
+      </c>
+      <c r="B25" s="5" t="inlineStr">
+        <is>
+          <t>04/06/2026</t>
+        </is>
+      </c>
+      <c r="C25" s="5" t="inlineStr">
+        <is>
+          <t>M. Ilyas</t>
+        </is>
+      </c>
+      <c r="D25" s="5" t="inlineStr">
+        <is>
+          <t>50y</t>
+        </is>
+      </c>
+      <c r="E25" s="5" t="inlineStr">
+        <is>
+          <t>Healthcard</t>
+        </is>
+      </c>
+      <c r="G25" s="5" t="inlineStr">
+        <is>
+          <t>Dr. Matti-ullah</t>
+        </is>
+      </c>
+      <c r="H25" s="5" t="inlineStr">
+        <is>
+          <t>C/Angio + PCI</t>
+        </is>
+      </c>
+      <c r="I25" s="5" t="n">
+        <v>194718</v>
+      </c>
+      <c r="J25" s="5" t="n">
+        <v>11650</v>
+      </c>
+      <c r="K25" s="5" t="n">
+        <v>183068</v>
+      </c>
+      <c r="N25" s="5" t="inlineStr">
+        <is>
+          <t>106000</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="5" t="n">
+        <v>21</v>
+      </c>
+      <c r="B26" s="5" t="inlineStr">
+        <is>
+          <t>04/06/2026</t>
+        </is>
+      </c>
+      <c r="C26" s="5" t="inlineStr">
+        <is>
+          <t>M. Islam</t>
+        </is>
+      </c>
+      <c r="D26" s="5" t="inlineStr">
+        <is>
+          <t>44y</t>
+        </is>
+      </c>
+      <c r="E26" s="5" t="inlineStr">
+        <is>
+          <t>Healthcard</t>
+        </is>
+      </c>
+      <c r="G26" s="5" t="inlineStr">
+        <is>
+          <t>Dr. Suleman Khan</t>
+        </is>
+      </c>
+      <c r="H26" s="5" t="inlineStr">
+        <is>
+          <t>C/Angio + PCI</t>
+        </is>
+      </c>
+      <c r="I26" s="5" t="n">
+        <v>343620</v>
+      </c>
+      <c r="J26" s="5" t="n">
+        <v>20542</v>
+      </c>
+      <c r="K26" s="5" t="n">
+        <v>323078</v>
+      </c>
+      <c r="N26" s="5" t="inlineStr">
+        <is>
+          <t>162000</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="5" t="n">
+        <v>22</v>
+      </c>
+      <c r="B27" s="5" t="inlineStr">
+        <is>
+          <t>05/06/2026</t>
+        </is>
+      </c>
+      <c r="C27" s="5" t="inlineStr">
+        <is>
+          <t>Farzana</t>
+        </is>
+      </c>
+      <c r="D27" s="5" t="inlineStr">
+        <is>
+          <t>54y</t>
+        </is>
+      </c>
+      <c r="E27" s="5" t="inlineStr">
+        <is>
+          <t>Healthcard</t>
+        </is>
+      </c>
+      <c r="G27" s="5" t="inlineStr">
+        <is>
+          <t>Dr. Suleman Khan</t>
+        </is>
+      </c>
+      <c r="H27" s="5" t="inlineStr">
+        <is>
+          <t>C/Angio</t>
+        </is>
+      </c>
+      <c r="I27" s="5" t="n">
+        <v>22908</v>
+      </c>
+      <c r="J27" s="5" t="n">
+        <v>1369</v>
+      </c>
+      <c r="K27" s="5" t="n">
+        <v>21539</v>
+      </c>
+      <c r="N27" s="5" t="inlineStr">
+        <is>
+          <t>9000</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="5" t="n">
+        <v>23</v>
+      </c>
+      <c r="B28" s="5" t="inlineStr">
+        <is>
+          <t>05/06/2026</t>
+        </is>
+      </c>
+      <c r="C28" s="5" t="inlineStr">
+        <is>
+          <t>Zafar Iqbal</t>
+        </is>
+      </c>
+      <c r="D28" s="5" t="inlineStr">
+        <is>
+          <t>56y</t>
+        </is>
+      </c>
+      <c r="E28" s="5" t="inlineStr">
+        <is>
+          <t>Healthcard</t>
+        </is>
+      </c>
+      <c r="G28" s="5" t="inlineStr">
+        <is>
+          <t>Dr. Suleman Khan</t>
+        </is>
+      </c>
+      <c r="H28" s="5" t="inlineStr">
+        <is>
+          <t>C/Angio</t>
+        </is>
+      </c>
+      <c r="I28" s="5" t="n">
+        <v>22908</v>
+      </c>
+      <c r="J28" s="5" t="n">
+        <v>1369</v>
+      </c>
+      <c r="K28" s="5" t="n">
+        <v>21539</v>
+      </c>
+      <c r="N28" s="5" t="inlineStr">
+        <is>
+          <t>11500</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="5" t="n">
+        <v>24</v>
+      </c>
+      <c r="B29" s="5" t="inlineStr">
+        <is>
+          <t>05/06/2026</t>
+        </is>
+      </c>
+      <c r="C29" s="5" t="inlineStr">
+        <is>
+          <t>M. Mushtaq</t>
+        </is>
+      </c>
+      <c r="D29" s="5" t="inlineStr">
+        <is>
+          <t>58y</t>
+        </is>
+      </c>
+      <c r="E29" s="5" t="inlineStr">
+        <is>
+          <t>Healthcard</t>
+        </is>
+      </c>
+      <c r="G29" s="5" t="inlineStr">
+        <is>
+          <t>Dr. Suleman Khan</t>
+        </is>
+      </c>
+      <c r="H29" s="5" t="inlineStr">
+        <is>
+          <t>C/Angio</t>
+        </is>
+      </c>
+      <c r="I29" s="5" t="n">
+        <v>22908</v>
+      </c>
+      <c r="J29" s="5" t="n">
+        <v>1369</v>
+      </c>
+      <c r="K29" s="5" t="n">
+        <v>21539</v>
+      </c>
+      <c r="N29" s="5" t="inlineStr">
+        <is>
+          <t>9000</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="5" t="n">
+        <v>25</v>
+      </c>
+      <c r="B30" s="5" t="inlineStr">
+        <is>
+          <t>05/06/2026</t>
+        </is>
+      </c>
+      <c r="C30" s="5" t="inlineStr">
+        <is>
+          <t>Imran</t>
+        </is>
+      </c>
+      <c r="D30" s="5" t="inlineStr">
+        <is>
+          <t>50y</t>
+        </is>
+      </c>
+      <c r="E30" s="5" t="inlineStr">
+        <is>
+          <t>Healthcard</t>
+        </is>
+      </c>
+      <c r="G30" s="5" t="inlineStr">
+        <is>
+          <t>Dr. Anjum Rana</t>
+        </is>
+      </c>
+      <c r="H30" s="5" t="inlineStr">
+        <is>
+          <t>C/Angio</t>
+        </is>
+      </c>
+      <c r="I30" s="5" t="n">
+        <v>22908</v>
+      </c>
+      <c r="J30" s="5" t="n">
+        <v>1369</v>
+      </c>
+      <c r="K30" s="5" t="n">
+        <v>21539</v>
+      </c>
+      <c r="N30" s="5" t="inlineStr">
+        <is>
+          <t>11500</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="5" t="n">
+        <v>26</v>
+      </c>
+      <c r="B31" s="5" t="inlineStr">
+        <is>
+          <t>05/06/2026</t>
+        </is>
+      </c>
+      <c r="C31" s="5" t="inlineStr">
+        <is>
+          <t>Arshad Mehmood</t>
+        </is>
+      </c>
+      <c r="D31" s="5" t="inlineStr">
+        <is>
+          <t>50y</t>
+        </is>
+      </c>
+      <c r="E31" s="5" t="inlineStr">
+        <is>
+          <t>Healthcard</t>
+        </is>
+      </c>
+      <c r="G31" s="5" t="inlineStr">
+        <is>
+          <t>Dr. Anjum Rana</t>
+        </is>
+      </c>
+      <c r="H31" s="5" t="inlineStr">
+        <is>
+          <t>C/Angio</t>
+        </is>
+      </c>
+      <c r="I31" s="5" t="n">
+        <v>22908</v>
+      </c>
+      <c r="J31" s="5" t="n">
+        <v>1369</v>
+      </c>
+      <c r="K31" s="5" t="n">
+        <v>21539</v>
+      </c>
+      <c r="N31" s="5" t="inlineStr">
+        <is>
+          <t>11500</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="5" t="n">
+        <v>27</v>
+      </c>
+      <c r="B32" s="5" t="inlineStr">
+        <is>
+          <t>05/06/2026</t>
+        </is>
+      </c>
+      <c r="C32" s="5" t="inlineStr">
+        <is>
+          <t>Abid Javeed</t>
+        </is>
+      </c>
+      <c r="D32" s="5" t="inlineStr">
+        <is>
+          <t>60y</t>
+        </is>
+      </c>
+      <c r="E32" s="5" t="inlineStr">
+        <is>
+          <t>Healthcard</t>
+        </is>
+      </c>
+      <c r="G32" s="5" t="inlineStr">
+        <is>
+          <t>Dr. Anjum Rana</t>
+        </is>
+      </c>
+      <c r="H32" s="5" t="inlineStr">
+        <is>
+          <t>C/Angio + PCI</t>
+        </is>
+      </c>
+      <c r="I32" s="5" t="n">
+        <v>340000</v>
+      </c>
+      <c r="J32" s="5" t="n">
+        <v>11650</v>
+      </c>
+      <c r="K32" s="5" t="n">
+        <v>328350</v>
+      </c>
+      <c r="N32" s="5" t="inlineStr">
+        <is>
+          <t>114500</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="5" t="n">
+        <v>28</v>
+      </c>
+      <c r="B33" s="5" t="inlineStr">
+        <is>
+          <t>05/06/2026</t>
+        </is>
+      </c>
+      <c r="C33" s="5" t="inlineStr">
+        <is>
+          <t>M. Arshad</t>
+        </is>
+      </c>
+      <c r="D33" s="5" t="inlineStr">
+        <is>
+          <t>46y</t>
+        </is>
+      </c>
+      <c r="E33" s="5" t="inlineStr">
+        <is>
+          <t>Healthcard</t>
+        </is>
+      </c>
+      <c r="G33" s="5" t="inlineStr">
+        <is>
+          <t>Dr. Anjum Rana</t>
+        </is>
+      </c>
+      <c r="H33" s="5" t="inlineStr">
+        <is>
+          <t>C/Angio + PCI</t>
+        </is>
+      </c>
+      <c r="I33" s="5" t="n">
+        <v>550000</v>
+      </c>
+      <c r="J33" s="5" t="n">
+        <v>17519</v>
+      </c>
+      <c r="K33" s="5" t="n">
+        <v>532481</v>
+      </c>
+      <c r="N33" s="5" t="inlineStr">
+        <is>
+          <t>183000</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="5" t="n">
+        <v>29</v>
+      </c>
+      <c r="B34" s="5" t="inlineStr">
+        <is>
+          <t>05/06/2026</t>
+        </is>
+      </c>
+      <c r="C34" s="5" t="inlineStr">
+        <is>
+          <t>Riffat</t>
+        </is>
+      </c>
+      <c r="D34" s="5" t="inlineStr">
+        <is>
+          <t>54y</t>
+        </is>
+      </c>
+      <c r="E34" s="5" t="inlineStr">
+        <is>
+          <t>Healthcard</t>
+        </is>
+      </c>
+      <c r="G34" s="5" t="inlineStr">
+        <is>
+          <t>Dr. Anjum Rana</t>
+        </is>
+      </c>
+      <c r="H34" s="5" t="inlineStr">
+        <is>
+          <t>C/Angio + PCI</t>
+        </is>
+      </c>
+      <c r="I34" s="5" t="n">
+        <v>194718</v>
+      </c>
+      <c r="J34" s="5" t="n">
+        <v>11650</v>
+      </c>
+      <c r="K34" s="5" t="n">
+        <v>183068</v>
+      </c>
+      <c r="N34" s="5" t="inlineStr">
+        <is>
+          <t>82500</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="5" t="n">
+        <v>30</v>
+      </c>
+      <c r="B35" s="5" t="inlineStr">
+        <is>
+          <t>06/06/2026</t>
+        </is>
+      </c>
+      <c r="C35" s="5" t="inlineStr">
+        <is>
+          <t>Raheela Saleem</t>
+        </is>
+      </c>
+      <c r="D35" s="5" t="inlineStr">
+        <is>
+          <t>63y</t>
+        </is>
+      </c>
+      <c r="E35" s="5" t="inlineStr">
+        <is>
+          <t>Healthcard</t>
+        </is>
+      </c>
+      <c r="G35" s="5" t="inlineStr">
+        <is>
+          <t>Dr. Kashif Zaffar</t>
+        </is>
+      </c>
+      <c r="H35" s="5" t="inlineStr">
+        <is>
+          <t>C/Angio</t>
+        </is>
+      </c>
+      <c r="I35" s="5" t="n">
+        <v>22908</v>
+      </c>
+      <c r="J35" s="5" t="n">
+        <v>1369</v>
+      </c>
+      <c r="K35" s="5" t="n">
+        <v>21539</v>
+      </c>
+      <c r="N35" s="5" t="inlineStr">
+        <is>
+          <t>11750</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="5" t="n">
+        <v>31</v>
+      </c>
+      <c r="B36" s="5" t="inlineStr">
+        <is>
+          <t>06/06/2026</t>
+        </is>
+      </c>
+      <c r="C36" s="5" t="inlineStr">
+        <is>
+          <t>Ruksana</t>
+        </is>
+      </c>
+      <c r="D36" s="5" t="inlineStr">
+        <is>
+          <t>70y</t>
+        </is>
+      </c>
+      <c r="E36" s="5" t="inlineStr">
+        <is>
+          <t>Healthcard</t>
+        </is>
+      </c>
+      <c r="G36" s="5" t="inlineStr">
+        <is>
+          <t>Dr. Suleman Khan</t>
+        </is>
+      </c>
+      <c r="H36" s="5" t="inlineStr">
+        <is>
+          <t>C/Angio</t>
+        </is>
+      </c>
+      <c r="I36" s="5" t="n">
+        <v>22908</v>
+      </c>
+      <c r="J36" s="5" t="n">
+        <v>1369</v>
+      </c>
+      <c r="K36" s="5" t="n">
+        <v>21539</v>
+      </c>
+      <c r="N36" s="5" t="inlineStr">
+        <is>
+          <t>11500</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="5" t="n">
+        <v>32</v>
+      </c>
+      <c r="B37" s="5" t="inlineStr">
+        <is>
+          <t>06/06/2026</t>
+        </is>
+      </c>
+      <c r="C37" s="5" t="inlineStr">
+        <is>
+          <t>Asma Khalid</t>
+        </is>
+      </c>
+      <c r="D37" s="5" t="inlineStr">
+        <is>
+          <t>40y</t>
+        </is>
+      </c>
+      <c r="E37" s="5" t="inlineStr">
+        <is>
+          <t>Healthcard</t>
+        </is>
+      </c>
+      <c r="G37" s="5" t="inlineStr">
+        <is>
+          <t>Dr. Suleman Khan</t>
+        </is>
+      </c>
+      <c r="H37" s="5" t="inlineStr">
+        <is>
+          <t>C/Angio</t>
+        </is>
+      </c>
+      <c r="I37" s="5" t="n">
+        <v>22908</v>
+      </c>
+      <c r="J37" s="5" t="n">
+        <v>1369</v>
+      </c>
+      <c r="K37" s="5" t="n">
+        <v>21539</v>
+      </c>
+      <c r="N37" s="5" t="inlineStr">
+        <is>
+          <t>11500</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="5" t="n">
+        <v>33</v>
+      </c>
+      <c r="B38" s="5" t="inlineStr">
+        <is>
+          <t>06/06/2026</t>
+        </is>
+      </c>
+      <c r="C38" s="5" t="inlineStr">
+        <is>
+          <t>M. Idrees</t>
+        </is>
+      </c>
+      <c r="D38" s="5" t="inlineStr">
+        <is>
+          <t>50y</t>
+        </is>
+      </c>
+      <c r="E38" s="5" t="inlineStr">
+        <is>
+          <t>Healthcard</t>
+        </is>
+      </c>
+      <c r="G38" s="5" t="inlineStr">
+        <is>
+          <t>Dr. Suleman Khan</t>
+        </is>
+      </c>
+      <c r="H38" s="5" t="inlineStr">
+        <is>
+          <t>C/Angio</t>
+        </is>
+      </c>
+      <c r="I38" s="5" t="n">
+        <v>22908</v>
+      </c>
+      <c r="J38" s="5" t="n">
+        <v>1369</v>
+      </c>
+      <c r="K38" s="5" t="n">
+        <v>21539</v>
+      </c>
+      <c r="N38" s="5" t="inlineStr">
+        <is>
+          <t>11500</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="5" t="n">
+        <v>34</v>
+      </c>
+      <c r="B39" s="5" t="inlineStr">
+        <is>
+          <t>06/06/2026</t>
+        </is>
+      </c>
+      <c r="C39" s="5" t="inlineStr">
+        <is>
+          <t>Saghir</t>
+        </is>
+      </c>
+      <c r="D39" s="5" t="inlineStr">
+        <is>
+          <t>66y</t>
+        </is>
+      </c>
+      <c r="E39" s="5" t="inlineStr">
+        <is>
+          <t>Healthcard</t>
+        </is>
+      </c>
+      <c r="G39" s="5" t="inlineStr">
+        <is>
+          <t>Dr. Anjum Rana</t>
+        </is>
+      </c>
+      <c r="H39" s="5" t="inlineStr">
+        <is>
+          <t>C/Angio + PCI</t>
+        </is>
+      </c>
+      <c r="I39" s="5" t="n">
+        <v>343620</v>
+      </c>
+      <c r="J39" s="5" t="n">
+        <v>20542</v>
+      </c>
+      <c r="K39" s="5" t="n">
+        <v>323078</v>
+      </c>
+      <c r="N39" s="5" t="inlineStr">
+        <is>
+          <t>183000</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="5" t="n">
+        <v>35</v>
+      </c>
+      <c r="B40" s="5" t="inlineStr">
+        <is>
+          <t>06/06/2026</t>
+        </is>
+      </c>
+      <c r="C40" s="5" t="inlineStr">
+        <is>
+          <t>Nadeem Aslam Khan</t>
+        </is>
+      </c>
+      <c r="D40" s="5" t="inlineStr">
+        <is>
+          <t>60y</t>
+        </is>
+      </c>
+      <c r="E40" s="5" t="inlineStr">
+        <is>
+          <t>Healthcard</t>
+        </is>
+      </c>
+      <c r="G40" s="5" t="inlineStr">
+        <is>
+          <t>Dr. Kashif Zaffar</t>
+        </is>
+      </c>
+      <c r="H40" s="5" t="inlineStr">
+        <is>
+          <t>C/Angio + PCI</t>
+        </is>
+      </c>
+      <c r="I40" s="5" t="n">
+        <v>194718</v>
+      </c>
+      <c r="J40" s="5" t="n">
+        <v>11650</v>
+      </c>
+      <c r="K40" s="5" t="n">
+        <v>183068</v>
+      </c>
+      <c r="N40" s="5" t="inlineStr">
+        <is>
+          <t>97000</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="5" t="n">
+        <v>36</v>
+      </c>
+      <c r="B41" s="5" t="inlineStr">
+        <is>
+          <t>06/06/2026</t>
+        </is>
+      </c>
+      <c r="C41" s="5" t="inlineStr">
+        <is>
+          <t>Muntazar</t>
+        </is>
+      </c>
+      <c r="D41" s="5" t="inlineStr">
+        <is>
+          <t>39y</t>
+        </is>
+      </c>
+      <c r="E41" s="5" t="inlineStr">
+        <is>
+          <t>Healthcard</t>
+        </is>
+      </c>
+      <c r="G41" s="5" t="inlineStr">
+        <is>
+          <t>Dr. Kashif Zaffar</t>
+        </is>
+      </c>
+      <c r="H41" s="5" t="inlineStr">
+        <is>
+          <t>C/Angio + PCI</t>
+        </is>
+      </c>
+      <c r="I41" s="5" t="n">
+        <v>286350</v>
+      </c>
+      <c r="J41" s="5" t="n">
+        <v>17519</v>
+      </c>
+      <c r="K41" s="5" t="n">
+        <v>268831</v>
+      </c>
+      <c r="N41" s="5" t="inlineStr">
+        <is>
+          <t>162850</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="5" t="n">
+        <v>37</v>
+      </c>
+      <c r="B42" s="5" t="inlineStr">
+        <is>
+          <t>06/06/2026</t>
+        </is>
+      </c>
+      <c r="C42" s="5" t="inlineStr">
+        <is>
+          <t>Balqees</t>
+        </is>
+      </c>
+      <c r="D42" s="5" t="inlineStr">
+        <is>
+          <t>60y</t>
+        </is>
+      </c>
+      <c r="E42" s="5" t="inlineStr">
+        <is>
+          <t>Healthcard</t>
+        </is>
+      </c>
+      <c r="G42" s="5" t="inlineStr">
+        <is>
+          <t>Dr. Matti-ullah</t>
+        </is>
+      </c>
+      <c r="H42" s="5" t="inlineStr">
+        <is>
+          <t>C/Angio + PCI</t>
+        </is>
+      </c>
+      <c r="I42" s="5" t="n">
+        <v>286350</v>
+      </c>
+      <c r="J42" s="5" t="n">
+        <v>17519</v>
+      </c>
+      <c r="K42" s="5" t="n">
+        <v>268831</v>
+      </c>
+      <c r="N42" s="5" t="inlineStr">
+        <is>
+          <t>168000</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="5" t="n">
+        <v>38</v>
+      </c>
+      <c r="B43" s="5" t="inlineStr">
+        <is>
+          <t>08/06/2026</t>
+        </is>
+      </c>
+      <c r="C43" s="5" t="inlineStr">
+        <is>
+          <t>Zareena</t>
+        </is>
+      </c>
+      <c r="D43" s="5" t="inlineStr">
+        <is>
+          <t>50y</t>
+        </is>
+      </c>
+      <c r="E43" s="5" t="inlineStr">
+        <is>
+          <t>Healthcard</t>
+        </is>
+      </c>
+      <c r="G43" s="5" t="inlineStr">
+        <is>
+          <t>Dr. Wali</t>
+        </is>
+      </c>
+      <c r="H43" s="5" t="inlineStr">
+        <is>
+          <t>C/Angio</t>
+        </is>
+      </c>
+      <c r="I43" s="5" t="n">
+        <v>22908</v>
+      </c>
+      <c r="J43" s="5" t="n">
+        <v>1369</v>
+      </c>
+      <c r="K43" s="5" t="n">
+        <v>21539</v>
+      </c>
+      <c r="N43" s="5" t="inlineStr">
+        <is>
+          <t>11500</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="5" t="n">
+        <v>39</v>
+      </c>
+      <c r="B44" s="5" t="inlineStr">
+        <is>
+          <t>08/06/2026</t>
+        </is>
+      </c>
+      <c r="C44" s="5" t="inlineStr">
+        <is>
+          <t>Bashir Ahmed</t>
+        </is>
+      </c>
+      <c r="D44" s="5" t="inlineStr">
+        <is>
+          <t>58y</t>
+        </is>
+      </c>
+      <c r="E44" s="5" t="inlineStr">
+        <is>
+          <t>Healthcard</t>
+        </is>
+      </c>
+      <c r="G44" s="5" t="inlineStr">
+        <is>
+          <t>Dr. Suleman Khan</t>
+        </is>
+      </c>
+      <c r="H44" s="5" t="inlineStr">
+        <is>
+          <t>C/Angio</t>
+        </is>
+      </c>
+      <c r="I44" s="5" t="n">
+        <v>22908</v>
+      </c>
+      <c r="J44" s="5" t="n">
+        <v>1369</v>
+      </c>
+      <c r="K44" s="5" t="n">
+        <v>21539</v>
+      </c>
+      <c r="N44" s="5" t="inlineStr">
+        <is>
+          <t>11500</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="5" t="n">
+        <v>40</v>
+      </c>
+      <c r="B45" s="5" t="inlineStr">
+        <is>
+          <t>08/06/2026</t>
+        </is>
+      </c>
+      <c r="C45" s="5" t="inlineStr">
+        <is>
+          <t>Riffat Imtiaz</t>
+        </is>
+      </c>
+      <c r="D45" s="5" t="inlineStr">
+        <is>
+          <t>60y</t>
+        </is>
+      </c>
+      <c r="E45" s="5" t="inlineStr">
+        <is>
+          <t>Healthcard</t>
+        </is>
+      </c>
+      <c r="G45" s="5" t="inlineStr">
+        <is>
+          <t>Dr. Kashif Zaffar</t>
+        </is>
+      </c>
+      <c r="H45" s="5" t="inlineStr">
+        <is>
+          <t>C/Angio</t>
+        </is>
+      </c>
+      <c r="I45" s="5" t="n">
+        <v>22908</v>
+      </c>
+      <c r="J45" s="5" t="n">
+        <v>1369</v>
+      </c>
+      <c r="K45" s="5" t="n">
+        <v>21539</v>
+      </c>
+      <c r="N45" s="5" t="inlineStr">
+        <is>
+          <t>11750</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="5" t="n">
+        <v>41</v>
+      </c>
+      <c r="B46" s="5" t="inlineStr">
+        <is>
+          <t>08/06/2026</t>
+        </is>
+      </c>
+      <c r="C46" s="5" t="inlineStr">
+        <is>
+          <t>Ghulam Jillani</t>
+        </is>
+      </c>
+      <c r="D46" s="5" t="inlineStr">
+        <is>
+          <t>63y</t>
+        </is>
+      </c>
+      <c r="E46" s="5" t="inlineStr">
+        <is>
+          <t>Healthcard</t>
+        </is>
+      </c>
+      <c r="G46" s="5" t="inlineStr">
+        <is>
+          <t>Dr. Anjum Rana</t>
+        </is>
+      </c>
+      <c r="H46" s="5" t="inlineStr">
+        <is>
+          <t>C/Angio</t>
+        </is>
+      </c>
+      <c r="I46" s="5" t="n">
+        <v>22908</v>
+      </c>
+      <c r="J46" s="5" t="n">
+        <v>1369</v>
+      </c>
+      <c r="K46" s="5" t="n">
+        <v>21539</v>
+      </c>
+      <c r="N46" s="5" t="inlineStr">
+        <is>
+          <t>11500</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="5" t="n">
+        <v>42</v>
+      </c>
+      <c r="B47" s="5" t="inlineStr">
+        <is>
+          <t>08/06/2026</t>
+        </is>
+      </c>
+      <c r="C47" s="5" t="inlineStr">
+        <is>
+          <t>Sakina Bibi</t>
+        </is>
+      </c>
+      <c r="D47" s="5" t="inlineStr">
+        <is>
+          <t>45y</t>
+        </is>
+      </c>
+      <c r="E47" s="5" t="inlineStr">
+        <is>
+          <t>Healthcard</t>
+        </is>
+      </c>
+      <c r="G47" s="5" t="inlineStr">
+        <is>
+          <t>Dr. Anjum Rana</t>
+        </is>
+      </c>
+      <c r="H47" s="5" t="inlineStr">
+        <is>
+          <t>C/Angio</t>
+        </is>
+      </c>
+      <c r="I47" s="5" t="n">
+        <v>22908</v>
+      </c>
+      <c r="J47" s="5" t="n">
+        <v>1369</v>
+      </c>
+      <c r="K47" s="5" t="n">
+        <v>21539</v>
+      </c>
+      <c r="N47" s="5" t="inlineStr">
+        <is>
+          <t>11500</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="5" t="n">
+        <v>43</v>
+      </c>
+      <c r="B48" s="5" t="inlineStr">
+        <is>
+          <t>08/06/2026</t>
+        </is>
+      </c>
+      <c r="C48" s="5" t="inlineStr">
+        <is>
+          <t>Perveen Akhtar</t>
+        </is>
+      </c>
+      <c r="D48" s="5" t="inlineStr">
+        <is>
+          <t>63y</t>
+        </is>
+      </c>
+      <c r="E48" s="5" t="inlineStr">
+        <is>
+          <t>Healthcard</t>
+        </is>
+      </c>
+      <c r="G48" s="5" t="inlineStr">
+        <is>
+          <t>Dr. Anjum Rana</t>
+        </is>
+      </c>
+      <c r="H48" s="5" t="inlineStr">
+        <is>
+          <t>C/Angio + PCI</t>
+        </is>
+      </c>
+      <c r="I48" s="5" t="n">
+        <v>194718</v>
+      </c>
+      <c r="J48" s="5" t="n">
+        <v>11650</v>
+      </c>
+      <c r="K48" s="5" t="n">
+        <v>183068</v>
+      </c>
+      <c r="N48" s="5" t="inlineStr">
+        <is>
+          <t>87000</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="5" t="n">
+        <v>44</v>
+      </c>
+      <c r="B49" s="5" t="inlineStr">
+        <is>
+          <t>08/06/2026</t>
+        </is>
+      </c>
+      <c r="C49" s="5" t="inlineStr">
+        <is>
+          <t>M. Younas</t>
+        </is>
+      </c>
+      <c r="D49" s="5" t="inlineStr">
+        <is>
+          <t>60y</t>
+        </is>
+      </c>
+      <c r="E49" s="5" t="inlineStr">
+        <is>
+          <t>Healthcard</t>
+        </is>
+      </c>
+      <c r="G49" s="5" t="inlineStr">
+        <is>
+          <t>Dr. Matti-ullah</t>
+        </is>
+      </c>
+      <c r="H49" s="5" t="inlineStr">
+        <is>
+          <t>C/Angio + PCI</t>
+        </is>
+      </c>
+      <c r="I49" s="5" t="n">
+        <v>194718</v>
+      </c>
+      <c r="J49" s="5" t="n">
+        <v>11650</v>
+      </c>
+      <c r="K49" s="5" t="n">
+        <v>183068</v>
+      </c>
+      <c r="N49" s="5" t="inlineStr">
+        <is>
+          <t>104000</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="5" t="n">
+        <v>45</v>
+      </c>
+      <c r="B50" s="5" t="inlineStr">
+        <is>
+          <t>09/06/2026</t>
+        </is>
+      </c>
+      <c r="C50" s="5" t="inlineStr">
+        <is>
+          <t>Kousar Perveen</t>
+        </is>
+      </c>
+      <c r="D50" s="5" t="inlineStr">
+        <is>
+          <t>54y</t>
+        </is>
+      </c>
+      <c r="E50" s="5" t="inlineStr">
+        <is>
+          <t>Healthcard</t>
+        </is>
+      </c>
+      <c r="G50" s="5" t="inlineStr">
+        <is>
+          <t>Dr. Suleman Khan</t>
+        </is>
+      </c>
+      <c r="H50" s="5" t="inlineStr">
+        <is>
+          <t>C/Angio + PCI</t>
+        </is>
+      </c>
+      <c r="I50" s="5" t="n">
+        <v>343620</v>
+      </c>
+      <c r="J50" s="5" t="n">
+        <v>20542</v>
+      </c>
+      <c r="K50" s="5" t="n">
+        <v>323078</v>
+      </c>
+      <c r="N50" s="5" t="inlineStr">
+        <is>
+          <t>185000</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="5" t="n">
+        <v>46</v>
+      </c>
+      <c r="B51" s="5" t="inlineStr">
+        <is>
+          <t>09/06/2026</t>
+        </is>
+      </c>
+      <c r="C51" s="5" t="inlineStr">
+        <is>
+          <t>Shameem</t>
+        </is>
+      </c>
+      <c r="D51" s="5" t="inlineStr">
+        <is>
+          <t>72y</t>
+        </is>
+      </c>
+      <c r="E51" s="5" t="inlineStr">
+        <is>
+          <t>Healthcard</t>
+        </is>
+      </c>
+      <c r="G51" s="5" t="inlineStr">
+        <is>
+          <t>Dr. Suleman Khan</t>
+        </is>
+      </c>
+      <c r="H51" s="5" t="inlineStr">
+        <is>
+          <t>C/Angio + PCI</t>
+        </is>
+      </c>
+      <c r="I51" s="5" t="n">
+        <v>194718</v>
+      </c>
+      <c r="J51" s="5" t="n">
+        <v>11650</v>
+      </c>
+      <c r="K51" s="5" t="n">
+        <v>183068</v>
+      </c>
+      <c r="N51" s="5" t="inlineStr">
+        <is>
+          <t>71500</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="5" t="n">
+        <v>47</v>
+      </c>
+      <c r="B52" s="5" t="inlineStr">
+        <is>
+          <t>09/06/2026</t>
+        </is>
+      </c>
+      <c r="C52" s="5" t="inlineStr">
+        <is>
+          <t>Saleem</t>
+        </is>
+      </c>
+      <c r="D52" s="5" t="inlineStr">
+        <is>
+          <t>67y</t>
+        </is>
+      </c>
+      <c r="E52" s="5" t="inlineStr">
+        <is>
+          <t>Healthcard</t>
+        </is>
+      </c>
+      <c r="G52" s="5" t="inlineStr">
+        <is>
+          <t>Dr. Anjum Rana</t>
+        </is>
+      </c>
+      <c r="H52" s="5" t="inlineStr">
+        <is>
+          <t>C/Angio + PCI</t>
+        </is>
+      </c>
+      <c r="I52" s="5" t="n">
+        <v>194718</v>
+      </c>
+      <c r="J52" s="5" t="n">
+        <v>11650</v>
+      </c>
+      <c r="K52" s="5" t="n">
+        <v>183068</v>
+      </c>
+      <c r="N52" s="5" t="inlineStr">
+        <is>
+          <t>93000</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="5" t="n">
+        <v>48</v>
+      </c>
+      <c r="B53" s="5" t="inlineStr">
+        <is>
+          <t>09/06/2026</t>
+        </is>
+      </c>
+      <c r="C53" s="5" t="inlineStr">
+        <is>
+          <t>Sakina Bibi</t>
+        </is>
+      </c>
+      <c r="D53" s="5" t="inlineStr">
+        <is>
+          <t>45y</t>
+        </is>
+      </c>
+      <c r="E53" s="5" t="inlineStr">
+        <is>
+          <t>Healthcard</t>
+        </is>
+      </c>
+      <c r="G53" s="5" t="inlineStr">
+        <is>
+          <t>Dr. Anjum Rana</t>
+        </is>
+      </c>
+      <c r="H53" s="5" t="inlineStr">
+        <is>
+          <t>C/Angio + PCI</t>
+        </is>
+      </c>
+      <c r="I53" s="5" t="n">
+        <v>173802</v>
+      </c>
+      <c r="J53" s="5" t="n">
+        <v>11650</v>
+      </c>
+      <c r="K53" s="5" t="n">
+        <v>162152</v>
+      </c>
+      <c r="N53" s="5" t="inlineStr">
+        <is>
+          <t>102500</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="5" t="n">
+        <v>49</v>
+      </c>
+      <c r="B54" s="5" t="inlineStr">
+        <is>
+          <t>09/06/2026</t>
+        </is>
+      </c>
+      <c r="C54" s="5" t="inlineStr">
+        <is>
+          <t>Riaz Ahmed</t>
+        </is>
+      </c>
+      <c r="D54" s="5" t="inlineStr">
+        <is>
+          <t>75y</t>
+        </is>
+      </c>
+      <c r="E54" s="5" t="inlineStr">
+        <is>
+          <t>Healthcard</t>
+        </is>
+      </c>
+      <c r="G54" s="5" t="inlineStr">
+        <is>
+          <t>Dr. Aqeel Malik</t>
+        </is>
+      </c>
+      <c r="H54" s="5" t="inlineStr">
+        <is>
+          <t>C/Angio + PCI + Plasty</t>
+        </is>
+      </c>
+      <c r="I54" s="5" t="n">
+        <v>475000</v>
+      </c>
+      <c r="J54" s="5" t="n">
+        <v>17519</v>
+      </c>
+      <c r="K54" s="5" t="n">
+        <v>457481</v>
+      </c>
+      <c r="N54" s="5" t="inlineStr">
+        <is>
+          <t>168500</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="5" t="n">
+        <v>50</v>
+      </c>
+      <c r="B55" s="5" t="inlineStr">
+        <is>
+          <t>10/06/2026</t>
+        </is>
+      </c>
+      <c r="C55" s="5" t="inlineStr">
+        <is>
+          <t>Syed Sabir</t>
+        </is>
+      </c>
+      <c r="D55" s="5" t="inlineStr">
+        <is>
+          <t>50y</t>
+        </is>
+      </c>
+      <c r="E55" s="5" t="inlineStr">
+        <is>
+          <t>Healthcard</t>
+        </is>
+      </c>
+      <c r="G55" s="5" t="inlineStr">
+        <is>
+          <t>Dr. Anjum Rana</t>
+        </is>
+      </c>
+      <c r="H55" s="5" t="inlineStr">
+        <is>
+          <t>C/Angio</t>
+        </is>
+      </c>
+      <c r="I55" s="5" t="n">
+        <v>22908</v>
+      </c>
+      <c r="J55" s="5" t="n">
+        <v>1369</v>
+      </c>
+      <c r="K55" s="5" t="n">
+        <v>21539</v>
+      </c>
+      <c r="N55" s="5" t="inlineStr">
+        <is>
+          <t>11500</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="5" t="n">
+        <v>51</v>
+      </c>
+      <c r="B56" s="5" t="inlineStr">
+        <is>
+          <t>10/06/2026</t>
+        </is>
+      </c>
+      <c r="C56" s="5" t="inlineStr">
+        <is>
+          <t>Bushra</t>
+        </is>
+      </c>
+      <c r="D56" s="5" t="inlineStr">
+        <is>
+          <t>50y</t>
+        </is>
+      </c>
+      <c r="E56" s="5" t="inlineStr">
+        <is>
+          <t>Healthcard</t>
+        </is>
+      </c>
+      <c r="G56" s="5" t="inlineStr">
+        <is>
+          <t>Dr. Anjum Rana</t>
+        </is>
+      </c>
+      <c r="H56" s="5" t="inlineStr">
+        <is>
+          <t>C/Angio</t>
+        </is>
+      </c>
+      <c r="I56" s="5" t="n">
+        <v>20000</v>
+      </c>
+      <c r="J56" s="5" t="n">
+        <v>1369</v>
+      </c>
+      <c r="K56" s="5" t="n">
+        <v>18631</v>
+      </c>
+      <c r="N56" s="5" t="inlineStr">
+        <is>
+          <t>3200</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="5" t="n">
+        <v>52</v>
+      </c>
+      <c r="B57" s="5" t="inlineStr">
+        <is>
+          <t>10/06/2026</t>
+        </is>
+      </c>
+      <c r="C57" s="5" t="inlineStr">
+        <is>
+          <t>Ashraf</t>
+        </is>
+      </c>
+      <c r="D57" s="5" t="inlineStr">
+        <is>
+          <t>59y</t>
+        </is>
+      </c>
+      <c r="E57" s="5" t="inlineStr">
+        <is>
+          <t>Healthcard</t>
+        </is>
+      </c>
+      <c r="G57" s="5" t="inlineStr">
+        <is>
+          <t>Dr. Suleman Khan</t>
+        </is>
+      </c>
+      <c r="H57" s="5" t="inlineStr">
+        <is>
+          <t>C/Angio</t>
+        </is>
+      </c>
+      <c r="I57" s="5" t="n">
+        <v>22908</v>
+      </c>
+      <c r="J57" s="5" t="n">
+        <v>1369</v>
+      </c>
+      <c r="K57" s="5" t="n">
+        <v>21539</v>
+      </c>
+      <c r="N57" s="5" t="inlineStr">
+        <is>
+          <t>9000</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="5" t="n">
+        <v>53</v>
+      </c>
+      <c r="B58" s="5" t="inlineStr">
+        <is>
+          <t>10/06/2026</t>
+        </is>
+      </c>
+      <c r="C58" s="5" t="inlineStr">
+        <is>
+          <t>Nadeem Abdul Kareem</t>
+        </is>
+      </c>
+      <c r="D58" s="5" t="inlineStr">
+        <is>
+          <t>51y</t>
+        </is>
+      </c>
+      <c r="E58" s="5" t="inlineStr">
+        <is>
+          <t>Healthcard</t>
+        </is>
+      </c>
+      <c r="G58" s="5" t="inlineStr">
+        <is>
+          <t>Dr. Mukarram Batti</t>
+        </is>
+      </c>
+      <c r="H58" s="5" t="inlineStr">
+        <is>
+          <t>C/Angio</t>
+        </is>
+      </c>
+      <c r="I58" s="5" t="n">
+        <v>22908</v>
+      </c>
+      <c r="J58" s="5" t="n">
+        <v>1369</v>
+      </c>
+      <c r="K58" s="5" t="n">
+        <v>21539</v>
+      </c>
+      <c r="N58" s="5" t="inlineStr">
+        <is>
+          <t>11750</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="5" t="n">
+        <v>54</v>
+      </c>
+      <c r="B59" s="5" t="inlineStr">
+        <is>
+          <t>10/06/2026</t>
+        </is>
+      </c>
+      <c r="C59" s="5" t="inlineStr">
+        <is>
+          <t>Iffat Bibi</t>
+        </is>
+      </c>
+      <c r="D59" s="5" t="inlineStr">
+        <is>
+          <t>50y</t>
+        </is>
+      </c>
+      <c r="E59" s="5" t="inlineStr">
+        <is>
+          <t>Healthcard</t>
+        </is>
+      </c>
+      <c r="G59" s="5" t="inlineStr">
+        <is>
+          <t>Dr. Matti-ullah</t>
+        </is>
+      </c>
+      <c r="H59" s="5" t="inlineStr">
+        <is>
+          <t>C/Angio</t>
+        </is>
+      </c>
+      <c r="I59" s="5" t="n">
+        <v>22908</v>
+      </c>
+      <c r="J59" s="5" t="n">
+        <v>1369</v>
+      </c>
+      <c r="K59" s="5" t="n">
+        <v>21539</v>
+      </c>
+      <c r="N59" s="5" t="inlineStr">
+        <is>
+          <t>11750</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="5" t="n">
+        <v>55</v>
+      </c>
+      <c r="B60" s="5" t="inlineStr">
+        <is>
+          <t>10/06/2026</t>
+        </is>
+      </c>
+      <c r="C60" s="5" t="inlineStr">
+        <is>
+          <t>Shahida Pervaiz</t>
+        </is>
+      </c>
+      <c r="D60" s="5" t="inlineStr">
+        <is>
+          <t>49y</t>
+        </is>
+      </c>
+      <c r="E60" s="5" t="inlineStr">
+        <is>
+          <t>Healthcard</t>
+        </is>
+      </c>
+      <c r="G60" s="5" t="inlineStr">
+        <is>
+          <t>Dr. Anjum Rana</t>
+        </is>
+      </c>
+      <c r="H60" s="5" t="inlineStr">
+        <is>
+          <t>C/Angio + PCI</t>
+        </is>
+      </c>
+      <c r="I60" s="5" t="n">
+        <v>286350</v>
+      </c>
+      <c r="J60" s="5" t="n">
+        <v>17519</v>
+      </c>
+      <c r="K60" s="5" t="n">
+        <v>268831</v>
+      </c>
+      <c r="N60" s="5" t="inlineStr">
+        <is>
+          <t>124000</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="5" t="n">
+        <v>56</v>
+      </c>
+      <c r="B61" s="5" t="inlineStr">
+        <is>
+          <t>10/06/2026</t>
+        </is>
+      </c>
+      <c r="C61" s="5" t="inlineStr">
+        <is>
+          <t>Ashiq Perveen</t>
+        </is>
+      </c>
+      <c r="D61" s="5" t="inlineStr">
+        <is>
+          <t>71y</t>
+        </is>
+      </c>
+      <c r="E61" s="5" t="inlineStr">
+        <is>
+          <t>Healthcard</t>
+        </is>
+      </c>
+      <c r="G61" s="5" t="inlineStr">
+        <is>
+          <t>Dr. Anjum Rana</t>
+        </is>
+      </c>
+      <c r="H61" s="5" t="inlineStr">
+        <is>
+          <t>C/Angio + PCI</t>
+        </is>
+      </c>
+      <c r="I61" s="5" t="n">
+        <v>750000</v>
+      </c>
+      <c r="J61" s="5" t="n">
+        <v>11650</v>
+      </c>
+      <c r="K61" s="5" t="n">
+        <v>738350</v>
+      </c>
+      <c r="N61" s="5" t="inlineStr">
+        <is>
+          <t>47000</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="5" t="n">
+        <v>57</v>
+      </c>
+      <c r="B62" s="5" t="inlineStr">
+        <is>
+          <t>10/06/2026</t>
+        </is>
+      </c>
+      <c r="C62" s="5" t="inlineStr">
+        <is>
+          <t>Humaira Bibi</t>
+        </is>
+      </c>
+      <c r="D62" s="5" t="inlineStr">
+        <is>
+          <t>54y</t>
+        </is>
+      </c>
+      <c r="E62" s="5" t="inlineStr">
+        <is>
+          <t>Healthcard</t>
+        </is>
+      </c>
+      <c r="G62" s="5" t="inlineStr">
+        <is>
+          <t>Dr. Suleman Khan</t>
+        </is>
+      </c>
+      <c r="H62" s="5" t="inlineStr">
+        <is>
+          <t>C/Angio + PCI</t>
+        </is>
+      </c>
+      <c r="I62" s="5" t="n">
+        <v>194718</v>
+      </c>
+      <c r="J62" s="5" t="n">
+        <v>11650</v>
+      </c>
+      <c r="K62" s="5" t="n">
+        <v>183068</v>
+      </c>
+      <c r="N62" s="5" t="inlineStr">
+        <is>
+          <t>84500</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="5" t="n">
+        <v>58</v>
+      </c>
+      <c r="B63" s="5" t="inlineStr">
+        <is>
+          <t>10/06/2026</t>
+        </is>
+      </c>
+      <c r="C63" s="5" t="inlineStr">
+        <is>
+          <t>Naheed Kausar</t>
+        </is>
+      </c>
+      <c r="D63" s="5" t="inlineStr">
+        <is>
+          <t>65y</t>
+        </is>
+      </c>
+      <c r="E63" s="5" t="inlineStr">
+        <is>
+          <t>Healthcard</t>
+        </is>
+      </c>
+      <c r="G63" s="5" t="inlineStr">
+        <is>
+          <t>Dr. Suleman Khan</t>
+        </is>
+      </c>
+      <c r="H63" s="5" t="inlineStr">
+        <is>
+          <t>C/Angio + PCI</t>
+        </is>
+      </c>
+      <c r="I63" s="5" t="n">
+        <v>286350</v>
+      </c>
+      <c r="J63" s="5" t="n">
+        <v>17519</v>
+      </c>
+      <c r="K63" s="5" t="n">
+        <v>268831</v>
+      </c>
+      <c r="N63" s="5" t="inlineStr">
+        <is>
+          <t>130000</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="5" t="n">
+        <v>59</v>
+      </c>
+      <c r="B64" s="5" t="inlineStr">
+        <is>
+          <t>10/06/2026</t>
+        </is>
+      </c>
+      <c r="C64" s="5" t="inlineStr">
+        <is>
+          <t>Haq Nawaz</t>
+        </is>
+      </c>
+      <c r="D64" s="5" t="inlineStr">
+        <is>
+          <t>46y</t>
+        </is>
+      </c>
+      <c r="E64" s="5" t="inlineStr">
+        <is>
+          <t>Healthcard</t>
+        </is>
+      </c>
+      <c r="G64" s="5" t="inlineStr">
+        <is>
+          <t>Dr. Suleman Khan</t>
+        </is>
+      </c>
+      <c r="H64" s="5" t="inlineStr">
+        <is>
+          <t>C/Angio + PCI</t>
+        </is>
+      </c>
+      <c r="I64" s="5" t="n">
+        <v>286350</v>
+      </c>
+      <c r="J64" s="5" t="n">
+        <v>17519</v>
+      </c>
+      <c r="K64" s="5" t="n">
+        <v>268831</v>
+      </c>
+      <c r="N64" s="5" t="inlineStr">
+        <is>
+          <t>154500</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="5" t="n">
+        <v>60</v>
+      </c>
+      <c r="B65" s="5" t="inlineStr">
+        <is>
+          <t>11/06/2026</t>
+        </is>
+      </c>
+      <c r="C65" s="5" t="inlineStr">
+        <is>
+          <t>M. Imran</t>
+        </is>
+      </c>
+      <c r="D65" s="5" t="inlineStr">
+        <is>
+          <t>44y</t>
+        </is>
+      </c>
+      <c r="E65" s="5" t="inlineStr">
+        <is>
+          <t>Healthcard</t>
+        </is>
+      </c>
+      <c r="G65" s="5" t="inlineStr">
+        <is>
+          <t>Dr. Anjum Rana</t>
+        </is>
+      </c>
+      <c r="H65" s="5" t="inlineStr">
+        <is>
+          <t>C/Angio</t>
+        </is>
+      </c>
+      <c r="I65" s="5" t="n">
+        <v>22908</v>
+      </c>
+      <c r="J65" s="5" t="n">
+        <v>1369</v>
+      </c>
+      <c r="K65" s="5" t="n">
+        <v>21539</v>
+      </c>
+      <c r="N65" s="5" t="inlineStr">
+        <is>
+          <t>11500</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="5" t="n">
+        <v>61</v>
+      </c>
+      <c r="B66" s="5" t="inlineStr">
+        <is>
+          <t>11/06/2026</t>
+        </is>
+      </c>
+      <c r="C66" s="5" t="inlineStr">
+        <is>
+          <t>Mrs. Safia</t>
+        </is>
+      </c>
+      <c r="D66" s="5" t="inlineStr">
+        <is>
+          <t>50y</t>
+        </is>
+      </c>
+      <c r="E66" s="5" t="inlineStr">
+        <is>
+          <t>Healthcard</t>
+        </is>
+      </c>
+      <c r="G66" s="5" t="inlineStr">
+        <is>
+          <t>Dr. Anjum Rana</t>
+        </is>
+      </c>
+      <c r="H66" s="5" t="inlineStr">
+        <is>
+          <t>C/Angio + PCI</t>
+        </is>
+      </c>
+      <c r="I66" s="5" t="n">
+        <v>286350</v>
+      </c>
+      <c r="J66" s="5" t="n">
+        <v>17519</v>
+      </c>
+      <c r="K66" s="5" t="n">
+        <v>268831</v>
+      </c>
+      <c r="N66" s="5" t="inlineStr">
+        <is>
+          <t>132500</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="5" t="n">
+        <v>62</v>
+      </c>
+      <c r="B67" s="5" t="inlineStr">
+        <is>
+          <t>11/06/2026</t>
+        </is>
+      </c>
+      <c r="C67" s="5" t="inlineStr">
+        <is>
+          <t>Shazia Bano</t>
+        </is>
+      </c>
+      <c r="D67" s="5" t="inlineStr">
+        <is>
+          <t>52y</t>
+        </is>
+      </c>
+      <c r="E67" s="5" t="inlineStr">
+        <is>
+          <t>Healthcard</t>
+        </is>
+      </c>
+      <c r="G67" s="5" t="inlineStr">
+        <is>
+          <t>Dr. Anjum Rana</t>
+        </is>
+      </c>
+      <c r="H67" s="5" t="inlineStr">
+        <is>
+          <t>C/Angio + PCI</t>
+        </is>
+      </c>
+      <c r="I67" s="5" t="n">
+        <v>286350</v>
+      </c>
+      <c r="J67" s="5" t="n">
+        <v>17519</v>
+      </c>
+      <c r="K67" s="5" t="n">
+        <v>268831</v>
+      </c>
+      <c r="N67" s="5" t="inlineStr">
+        <is>
+          <t>140500</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="5" t="n">
+        <v>63</v>
+      </c>
+      <c r="B68" s="5" t="inlineStr">
+        <is>
+          <t>11/06/2026</t>
+        </is>
+      </c>
+      <c r="C68" s="5" t="inlineStr">
+        <is>
+          <t>Zahid Yaseen</t>
+        </is>
+      </c>
+      <c r="D68" s="5" t="inlineStr">
+        <is>
+          <t>59y</t>
+        </is>
+      </c>
+      <c r="E68" s="5" t="inlineStr">
+        <is>
+          <t>Healthcard</t>
+        </is>
+      </c>
+      <c r="G68" s="5" t="inlineStr">
+        <is>
+          <t>Dr. Anjum Rana</t>
+        </is>
+      </c>
+      <c r="H68" s="5" t="inlineStr">
+        <is>
+          <t>C/Angio + PCI + Plasty</t>
+        </is>
+      </c>
+      <c r="I68" s="5" t="n">
+        <v>55200</v>
+      </c>
+      <c r="J68" s="5" t="n">
+        <v>1369</v>
+      </c>
+      <c r="K68" s="5" t="n">
+        <v>53831</v>
+      </c>
+      <c r="N68" s="5" t="inlineStr">
+        <is>
+          <t>43000</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="5" t="n">
+        <v>64</v>
+      </c>
+      <c r="B69" s="5" t="inlineStr">
+        <is>
+          <t>12/06/2026</t>
+        </is>
+      </c>
+      <c r="C69" s="5" t="inlineStr">
+        <is>
+          <t>Amanullah</t>
+        </is>
+      </c>
+      <c r="D69" s="5" t="inlineStr">
+        <is>
+          <t>50y</t>
+        </is>
+      </c>
+      <c r="E69" s="5" t="inlineStr">
+        <is>
+          <t>Healthcard</t>
+        </is>
+      </c>
+      <c r="G69" s="5" t="inlineStr">
+        <is>
+          <t>Dr. Suleman Khan</t>
+        </is>
+      </c>
+      <c r="H69" s="5" t="inlineStr">
+        <is>
+          <t>C/Angio + PCI</t>
+        </is>
+      </c>
+      <c r="I69" s="5" t="n">
+        <v>194718</v>
+      </c>
+      <c r="J69" s="5" t="n">
+        <v>11650</v>
+      </c>
+      <c r="K69" s="5" t="n">
+        <v>183068</v>
+      </c>
+      <c r="N69" s="5" t="inlineStr">
+        <is>
+          <t>67500</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="5" t="n">
+        <v>65</v>
+      </c>
+      <c r="B70" s="5" t="inlineStr">
+        <is>
+          <t>12/06/2026</t>
+        </is>
+      </c>
+      <c r="C70" s="5" t="inlineStr">
+        <is>
+          <t>M. Abbas</t>
+        </is>
+      </c>
+      <c r="D70" s="5" t="inlineStr">
+        <is>
+          <t>78y</t>
+        </is>
+      </c>
+      <c r="E70" s="5" t="inlineStr">
+        <is>
+          <t>Healthcard</t>
+        </is>
+      </c>
+      <c r="G70" s="5" t="inlineStr">
+        <is>
+          <t>Dr. Anjum Rana</t>
+        </is>
+      </c>
+      <c r="H70" s="5" t="inlineStr">
+        <is>
+          <t>C/Angio + PCI</t>
+        </is>
+      </c>
+      <c r="I70" s="5" t="n">
+        <v>194718</v>
+      </c>
+      <c r="J70" s="5" t="n">
+        <v>11650</v>
+      </c>
+      <c r="K70" s="5" t="n">
+        <v>183068</v>
+      </c>
+      <c r="N70" s="5" t="inlineStr">
+        <is>
+          <t>80500</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="5" t="n">
+        <v>66</v>
+      </c>
+      <c r="B71" s="5" t="inlineStr">
+        <is>
+          <t>13/06/2026</t>
+        </is>
+      </c>
+      <c r="C71" s="5" t="inlineStr">
+        <is>
+          <t>Farhan</t>
+        </is>
+      </c>
+      <c r="D71" s="5" t="inlineStr">
+        <is>
+          <t>37y</t>
+        </is>
+      </c>
+      <c r="E71" s="5" t="inlineStr">
+        <is>
+          <t>Healthcard</t>
+        </is>
+      </c>
+      <c r="G71" s="5" t="inlineStr">
+        <is>
+          <t>Dr. Anjum Rana</t>
+        </is>
+      </c>
+      <c r="H71" s="5" t="inlineStr">
+        <is>
+          <t>C/Angio</t>
+        </is>
+      </c>
+      <c r="I71" s="5" t="n">
+        <v>22908</v>
+      </c>
+      <c r="J71" s="5" t="n">
+        <v>1369</v>
+      </c>
+      <c r="K71" s="5" t="n">
+        <v>21539</v>
+      </c>
+      <c r="N71" s="5" t="inlineStr">
+        <is>
+          <t>11500</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="5" t="n">
+        <v>67</v>
+      </c>
+      <c r="B72" s="5" t="inlineStr">
+        <is>
+          <t>13/06/2026</t>
+        </is>
+      </c>
+      <c r="C72" s="5" t="inlineStr">
+        <is>
+          <t>M. Mansha</t>
+        </is>
+      </c>
+      <c r="D72" s="5" t="inlineStr">
+        <is>
+          <t>46y</t>
+        </is>
+      </c>
+      <c r="E72" s="5" t="inlineStr">
+        <is>
+          <t>Healthcard</t>
+        </is>
+      </c>
+      <c r="G72" s="5" t="inlineStr">
+        <is>
+          <t>Dr. Suleman Khan</t>
+        </is>
+      </c>
+      <c r="H72" s="5" t="inlineStr">
+        <is>
+          <t>C/Angio</t>
+        </is>
+      </c>
+      <c r="I72" s="5" t="n">
+        <v>22908</v>
+      </c>
+      <c r="J72" s="5" t="n">
+        <v>1369</v>
+      </c>
+      <c r="K72" s="5" t="n">
+        <v>21539</v>
+      </c>
+      <c r="N72" s="5" t="inlineStr">
+        <is>
+          <t>11500</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="5" t="n">
+        <v>68</v>
+      </c>
+      <c r="B73" s="5" t="inlineStr">
+        <is>
+          <t>13/06/2026</t>
+        </is>
+      </c>
+      <c r="C73" s="5" t="inlineStr">
+        <is>
+          <t>Rasheeda Begum</t>
+        </is>
+      </c>
+      <c r="D73" s="5" t="inlineStr">
+        <is>
+          <t>62y</t>
+        </is>
+      </c>
+      <c r="E73" s="5" t="inlineStr">
+        <is>
+          <t>Healthcard</t>
+        </is>
+      </c>
+      <c r="G73" s="5" t="inlineStr">
+        <is>
+          <t>Dr. Kashif Zaffar</t>
+        </is>
+      </c>
+      <c r="H73" s="5" t="inlineStr">
+        <is>
+          <t>C/Angio</t>
+        </is>
+      </c>
+      <c r="I73" s="5" t="n">
+        <v>22908</v>
+      </c>
+      <c r="J73" s="5" t="n">
+        <v>1369</v>
+      </c>
+      <c r="K73" s="5" t="n">
+        <v>21539</v>
+      </c>
+      <c r="N73" s="5" t="inlineStr">
+        <is>
+          <t>11750</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="5" t="n">
+        <v>69</v>
+      </c>
+      <c r="B74" s="5" t="inlineStr">
+        <is>
+          <t>13/06/2026</t>
+        </is>
+      </c>
+      <c r="C74" s="5" t="inlineStr">
+        <is>
+          <t>M. Ali Akhtar</t>
+        </is>
+      </c>
+      <c r="D74" s="5" t="inlineStr">
+        <is>
+          <t>46y</t>
+        </is>
+      </c>
+      <c r="E74" s="5" t="inlineStr">
+        <is>
+          <t>Healthcard</t>
+        </is>
+      </c>
+      <c r="G74" s="5" t="inlineStr">
+        <is>
+          <t>Dr. Ali Khawaja</t>
+        </is>
+      </c>
+      <c r="H74" s="5" t="inlineStr">
+        <is>
+          <t>C/Angio + PCI</t>
+        </is>
+      </c>
+      <c r="I74" s="5" t="n">
+        <v>194718</v>
+      </c>
+      <c r="J74" s="5" t="n">
+        <v>11650</v>
+      </c>
+      <c r="K74" s="5" t="n">
+        <v>183068</v>
+      </c>
+      <c r="N74" s="5" t="inlineStr">
+        <is>
+          <t>83600</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="5" t="n">
+        <v>70</v>
+      </c>
+      <c r="B75" s="5" t="inlineStr">
+        <is>
+          <t>13/06/2026</t>
+        </is>
+      </c>
+      <c r="C75" s="5" t="inlineStr">
+        <is>
+          <t>Naseem Begum</t>
+        </is>
+      </c>
+      <c r="D75" s="5" t="inlineStr">
+        <is>
+          <t>70y</t>
+        </is>
+      </c>
+      <c r="E75" s="5" t="inlineStr">
+        <is>
+          <t>Healthcard</t>
+        </is>
+      </c>
+      <c r="G75" s="5" t="inlineStr">
+        <is>
+          <t>Dr. Anjum Rana</t>
+        </is>
+      </c>
+      <c r="H75" s="5" t="inlineStr">
+        <is>
+          <t>C/Angio + PCI</t>
+        </is>
+      </c>
+      <c r="I75" s="5" t="n">
+        <v>286350</v>
+      </c>
+      <c r="J75" s="5" t="n">
+        <v>17519</v>
+      </c>
+      <c r="K75" s="5" t="n">
+        <v>268831</v>
+      </c>
+      <c r="N75" s="5" t="inlineStr">
+        <is>
+          <t>128500</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="5" t="n">
+        <v>71</v>
+      </c>
+      <c r="B76" s="5" t="inlineStr">
+        <is>
+          <t>13/06/2026</t>
+        </is>
+      </c>
+      <c r="C76" s="5" t="inlineStr">
+        <is>
+          <t>M. Younas</t>
+        </is>
+      </c>
+      <c r="D76" s="5" t="inlineStr">
+        <is>
+          <t>55y</t>
+        </is>
+      </c>
+      <c r="E76" s="5" t="inlineStr">
+        <is>
+          <t>Healthcard</t>
+        </is>
+      </c>
+      <c r="G76" s="5" t="inlineStr">
+        <is>
+          <t>Dr. Anjum Rana</t>
+        </is>
+      </c>
+      <c r="H76" s="5" t="inlineStr">
+        <is>
+          <t>C/Angio + PCI</t>
+        </is>
+      </c>
+      <c r="I76" s="5" t="n">
+        <v>286350</v>
+      </c>
+      <c r="J76" s="5" t="n">
+        <v>17519</v>
+      </c>
+      <c r="K76" s="5" t="n">
+        <v>268831</v>
+      </c>
+      <c r="N76" s="5" t="inlineStr">
+        <is>
+          <t>122000</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="5" t="n">
+        <v>72</v>
+      </c>
+      <c r="B77" s="5" t="inlineStr">
+        <is>
+          <t>13/06/2026</t>
+        </is>
+      </c>
+      <c r="C77" s="5" t="inlineStr">
+        <is>
+          <t>Ghulam Nabi</t>
+        </is>
+      </c>
+      <c r="D77" s="5" t="inlineStr">
+        <is>
+          <t>54y</t>
+        </is>
+      </c>
+      <c r="E77" s="5" t="inlineStr">
+        <is>
+          <t>Healthcard</t>
+        </is>
+      </c>
+      <c r="G77" s="5" t="inlineStr">
+        <is>
+          <t>Dr. Anjum Rana</t>
+        </is>
+      </c>
+      <c r="H77" s="5" t="inlineStr">
+        <is>
+          <t>C/Angio + PCI</t>
+        </is>
+      </c>
+      <c r="I77" s="5" t="n">
+        <v>286350</v>
+      </c>
+      <c r="J77" s="5" t="n">
+        <v>17519</v>
+      </c>
+      <c r="K77" s="5" t="n">
+        <v>268831</v>
+      </c>
+      <c r="N77" s="5" t="inlineStr">
+        <is>
+          <t>120500</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="5" t="n">
+        <v>73</v>
+      </c>
+      <c r="B78" s="5" t="inlineStr">
+        <is>
+          <t>13/06/2026</t>
+        </is>
+      </c>
+      <c r="C78" s="5" t="inlineStr">
+        <is>
+          <t>Tanveer Ahmad</t>
+        </is>
+      </c>
+      <c r="D78" s="5" t="inlineStr">
+        <is>
+          <t>51y</t>
+        </is>
+      </c>
+      <c r="E78" s="5" t="inlineStr">
+        <is>
+          <t>Healthcard</t>
+        </is>
+      </c>
+      <c r="G78" s="5" t="inlineStr">
+        <is>
+          <t>Dr. Kashif Zaffar</t>
+        </is>
+      </c>
+      <c r="H78" s="5" t="inlineStr">
+        <is>
+          <t>C/Angio + PCI</t>
+        </is>
+      </c>
+      <c r="I78" s="5" t="n">
+        <v>173804</v>
+      </c>
+      <c r="J78" s="5" t="n">
+        <v>11650</v>
+      </c>
+      <c r="K78" s="5" t="n">
+        <v>162154</v>
+      </c>
+      <c r="N78" s="5" t="inlineStr">
+        <is>
+          <t>95500</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="5" t="n">
+        <v>74</v>
+      </c>
+      <c r="B79" s="5" t="inlineStr">
+        <is>
+          <t>15/06/2026</t>
+        </is>
+      </c>
+      <c r="C79" s="5" t="inlineStr">
+        <is>
+          <t>Parveen Akhtar</t>
+        </is>
+      </c>
+      <c r="D79" s="5" t="inlineStr">
+        <is>
+          <t>60y</t>
+        </is>
+      </c>
+      <c r="E79" s="5" t="inlineStr">
+        <is>
+          <t>Healthcard</t>
+        </is>
+      </c>
+      <c r="G79" s="5" t="inlineStr">
+        <is>
+          <t>Dr. Kashif Zaffar</t>
+        </is>
+      </c>
+      <c r="H79" s="5" t="inlineStr">
+        <is>
+          <t>C/Angio</t>
+        </is>
+      </c>
+      <c r="I79" s="5" t="n">
+        <v>22908</v>
+      </c>
+      <c r="J79" s="5" t="n">
+        <v>1369</v>
+      </c>
+      <c r="K79" s="5" t="n">
+        <v>21539</v>
+      </c>
+      <c r="N79" s="5" t="inlineStr">
+        <is>
+          <t>11750</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="5" t="n">
+        <v>75</v>
+      </c>
+      <c r="B80" s="5" t="inlineStr">
+        <is>
+          <t>15/06/2026</t>
+        </is>
+      </c>
+      <c r="C80" s="5" t="inlineStr">
+        <is>
+          <t>Shabir Ahmad</t>
+        </is>
+      </c>
+      <c r="D80" s="5" t="inlineStr">
+        <is>
+          <t>50y</t>
+        </is>
+      </c>
+      <c r="E80" s="5" t="inlineStr">
+        <is>
+          <t>Healthcard</t>
+        </is>
+      </c>
+      <c r="G80" s="5" t="inlineStr">
+        <is>
+          <t>Dr. Suleman Khan</t>
+        </is>
+      </c>
+      <c r="H80" s="5" t="inlineStr">
+        <is>
+          <t>C/Angio</t>
+        </is>
+      </c>
+      <c r="I80" s="5" t="n">
+        <v>22908</v>
+      </c>
+      <c r="J80" s="5" t="n">
+        <v>1369</v>
+      </c>
+      <c r="K80" s="5" t="n">
+        <v>21539</v>
+      </c>
+      <c r="N80" s="5" t="inlineStr">
+        <is>
+          <t>11500</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="5" t="n">
+        <v>76</v>
+      </c>
+      <c r="B81" s="5" t="inlineStr">
+        <is>
+          <t>15/06/2026</t>
+        </is>
+      </c>
+      <c r="C81" s="5" t="inlineStr">
+        <is>
+          <t>Safia Bibi</t>
+        </is>
+      </c>
+      <c r="D81" s="5" t="inlineStr">
+        <is>
+          <t>72y</t>
+        </is>
+      </c>
+      <c r="E81" s="5" t="inlineStr">
+        <is>
+          <t>Healthcard</t>
+        </is>
+      </c>
+      <c r="G81" s="5" t="inlineStr">
+        <is>
+          <t>Dr. Anjum Rana</t>
+        </is>
+      </c>
+      <c r="H81" s="5" t="inlineStr">
+        <is>
+          <t>C/Angio + PCI</t>
+        </is>
+      </c>
+      <c r="I81" s="5" t="n">
+        <v>194718</v>
+      </c>
+      <c r="J81" s="5" t="n">
+        <v>11650</v>
+      </c>
+      <c r="K81" s="5" t="n">
+        <v>183068</v>
+      </c>
+      <c r="N81" s="5" t="inlineStr">
+        <is>
+          <t>78000</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="5" t="n">
+        <v>77</v>
+      </c>
+      <c r="B82" s="5" t="inlineStr">
+        <is>
+          <t>15/06/2026</t>
+        </is>
+      </c>
+      <c r="C82" s="5" t="inlineStr">
+        <is>
+          <t>Farhan Mani</t>
+        </is>
+      </c>
+      <c r="D82" s="5" t="inlineStr">
+        <is>
+          <t>57y</t>
+        </is>
+      </c>
+      <c r="E82" s="5" t="inlineStr">
+        <is>
+          <t>Healthcard</t>
+        </is>
+      </c>
+      <c r="G82" s="5" t="inlineStr">
+        <is>
+          <t>Dr. Anjum Rana</t>
+        </is>
+      </c>
+      <c r="H82" s="5" t="inlineStr">
+        <is>
+          <t>C/Angio + PCI</t>
+        </is>
+      </c>
+      <c r="I82" s="5" t="n">
+        <v>286350</v>
+      </c>
+      <c r="J82" s="5" t="n">
+        <v>17519</v>
+      </c>
+      <c r="K82" s="5" t="n">
+        <v>268831</v>
+      </c>
+      <c r="N82" s="5" t="inlineStr">
+        <is>
+          <t>141000</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="5" t="n">
+        <v>78</v>
+      </c>
+      <c r="B83" s="5" t="inlineStr">
+        <is>
+          <t>15/06/2026</t>
+        </is>
+      </c>
+      <c r="C83" s="5" t="inlineStr">
+        <is>
+          <t>Zahid Yaseen</t>
+        </is>
+      </c>
+      <c r="D83" s="5" t="inlineStr">
+        <is>
+          <t>59y</t>
+        </is>
+      </c>
+      <c r="E83" s="5" t="inlineStr">
+        <is>
+          <t>Healthcard</t>
+        </is>
+      </c>
+      <c r="G83" s="5" t="inlineStr">
+        <is>
+          <t>Dr. Anjum Rana</t>
+        </is>
+      </c>
+      <c r="H83" s="5" t="inlineStr">
+        <is>
+          <t>C/Angio + PCI</t>
+        </is>
+      </c>
+      <c r="I83" s="5" t="n">
+        <v>710000</v>
+      </c>
+      <c r="J83" s="5" t="n">
+        <v>11650</v>
+      </c>
+      <c r="K83" s="5" t="n">
+        <v>698350</v>
+      </c>
+      <c r="N83" s="5" t="inlineStr">
+        <is>
+          <t>71160</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="5" t="n">
+        <v>79</v>
+      </c>
+      <c r="B84" s="5" t="inlineStr">
+        <is>
+          <t>15/06/2026</t>
+        </is>
+      </c>
+      <c r="C84" s="5" t="inlineStr">
+        <is>
+          <t>Asmat Bibi</t>
+        </is>
+      </c>
+      <c r="D84" s="5" t="inlineStr">
+        <is>
+          <t>51y</t>
+        </is>
+      </c>
+      <c r="E84" s="5" t="inlineStr">
+        <is>
+          <t>Healthcard</t>
+        </is>
+      </c>
+      <c r="G84" s="5" t="inlineStr">
+        <is>
+          <t>Dr. Suleman Khan</t>
+        </is>
+      </c>
+      <c r="H84" s="5" t="inlineStr">
+        <is>
+          <t>C/Angio + PCI + Plasty</t>
+        </is>
+      </c>
+      <c r="I84" s="5" t="n">
+        <v>343620</v>
+      </c>
+      <c r="J84" s="5" t="n">
+        <v>20542</v>
+      </c>
+      <c r="K84" s="5" t="n">
+        <v>323078</v>
+      </c>
+      <c r="N84" s="5" t="inlineStr">
+        <is>
+          <t>185000</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="5" t="n">
+        <v>80</v>
+      </c>
+      <c r="B85" s="5" t="inlineStr">
+        <is>
+          <t>16/06/2026</t>
+        </is>
+      </c>
+      <c r="C85" s="5" t="inlineStr">
+        <is>
+          <t>Munawar Ali</t>
+        </is>
+      </c>
+      <c r="D85" s="5" t="inlineStr">
+        <is>
+          <t>51y</t>
+        </is>
+      </c>
+      <c r="E85" s="5" t="inlineStr">
+        <is>
+          <t>Healthcard</t>
+        </is>
+      </c>
+      <c r="G85" s="5" t="inlineStr">
+        <is>
+          <t>Dr. Anjum Rana</t>
+        </is>
+      </c>
+      <c r="H85" s="5" t="inlineStr">
+        <is>
+          <t>C/Angio</t>
+        </is>
+      </c>
+      <c r="I85" s="5" t="n">
+        <v>22908</v>
+      </c>
+      <c r="J85" s="5" t="n">
+        <v>1369</v>
+      </c>
+      <c r="K85" s="5" t="n">
+        <v>21539</v>
+      </c>
+      <c r="N85" s="5" t="inlineStr">
+        <is>
+          <t>11500</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="5" t="n">
+        <v>81</v>
+      </c>
+      <c r="B86" s="5" t="inlineStr">
+        <is>
+          <t>16/06/2026</t>
+        </is>
+      </c>
+      <c r="C86" s="5" t="inlineStr">
+        <is>
+          <t>Tasadeeq</t>
+        </is>
+      </c>
+      <c r="D86" s="5" t="inlineStr">
+        <is>
+          <t>50y</t>
+        </is>
+      </c>
+      <c r="E86" s="5" t="inlineStr">
+        <is>
+          <t>Healthcard</t>
+        </is>
+      </c>
+      <c r="G86" s="5" t="inlineStr">
+        <is>
+          <t>Dr. Suleman Khan</t>
+        </is>
+      </c>
+      <c r="H86" s="5" t="inlineStr">
+        <is>
+          <t>C/Angio</t>
+        </is>
+      </c>
+      <c r="I86" s="5" t="n">
+        <v>22908</v>
+      </c>
+      <c r="J86" s="5" t="n">
+        <v>1369</v>
+      </c>
+      <c r="K86" s="5" t="n">
+        <v>21539</v>
+      </c>
+      <c r="N86" s="5" t="inlineStr">
+        <is>
+          <t>11500</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="5" t="n">
+        <v>82</v>
+      </c>
+      <c r="B87" s="5" t="inlineStr">
+        <is>
+          <t>16/06/2026</t>
+        </is>
+      </c>
+      <c r="C87" s="5" t="inlineStr">
+        <is>
+          <t>Sarwar Bibi</t>
+        </is>
+      </c>
+      <c r="D87" s="5" t="inlineStr">
+        <is>
+          <t>50y</t>
+        </is>
+      </c>
+      <c r="E87" s="5" t="inlineStr">
+        <is>
+          <t>Healthcard</t>
+        </is>
+      </c>
+      <c r="G87" s="5" t="inlineStr">
+        <is>
+          <t>Dr. Anjum Rana</t>
+        </is>
+      </c>
+      <c r="H87" s="5" t="inlineStr">
+        <is>
+          <t>C/Angio + PCI</t>
+        </is>
+      </c>
+      <c r="I87" s="5" t="n">
+        <v>435000</v>
+      </c>
+      <c r="J87" s="5" t="n">
+        <v>11650</v>
+      </c>
+      <c r="K87" s="5" t="n">
+        <v>423350</v>
+      </c>
+      <c r="N87" s="5" t="inlineStr">
+        <is>
+          <t>78300</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="5" t="n">
+        <v>83</v>
+      </c>
+      <c r="B88" s="5" t="inlineStr">
+        <is>
+          <t>16/06/2026</t>
+        </is>
+      </c>
+      <c r="C88" s="5" t="inlineStr">
+        <is>
+          <t>Warfam</t>
+        </is>
+      </c>
+      <c r="D88" s="5" t="inlineStr">
+        <is>
+          <t>46y</t>
+        </is>
+      </c>
+      <c r="E88" s="5" t="inlineStr">
+        <is>
+          <t>Healthcard</t>
+        </is>
+      </c>
+      <c r="G88" s="5" t="inlineStr">
+        <is>
+          <t>Dr. Suleman Khan</t>
+        </is>
+      </c>
+      <c r="H88" s="5" t="inlineStr">
+        <is>
+          <t>C/Angio + PCI</t>
+        </is>
+      </c>
+      <c r="I88" s="5" t="n">
+        <v>194718</v>
+      </c>
+      <c r="J88" s="5" t="n">
+        <v>11650</v>
+      </c>
+      <c r="K88" s="5" t="n">
+        <v>183068</v>
+      </c>
+      <c r="N88" s="5" t="inlineStr">
+        <is>
+          <t>93000</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="5" t="n">
+        <v>84</v>
+      </c>
+      <c r="B89" s="5" t="inlineStr">
+        <is>
+          <t>17/06/2026</t>
+        </is>
+      </c>
+      <c r="C89" s="5" t="inlineStr">
+        <is>
+          <t>Khudabaksh</t>
+        </is>
+      </c>
+      <c r="D89" s="5" t="inlineStr">
+        <is>
+          <t>50y</t>
+        </is>
+      </c>
+      <c r="E89" s="5" t="inlineStr">
+        <is>
+          <t>Healthcard</t>
+        </is>
+      </c>
+      <c r="G89" s="5" t="inlineStr">
+        <is>
+          <t>Dr. Kashif Zaffar</t>
+        </is>
+      </c>
+      <c r="H89" s="5" t="inlineStr">
+        <is>
+          <t>C/Angio</t>
+        </is>
+      </c>
+      <c r="I89" s="5" t="n">
+        <v>22908</v>
+      </c>
+      <c r="J89" s="5" t="n">
+        <v>1369</v>
+      </c>
+      <c r="K89" s="5" t="n">
+        <v>21539</v>
+      </c>
+      <c r="N89" s="5" t="inlineStr">
+        <is>
+          <t>11750</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="5" t="n">
+        <v>85</v>
+      </c>
+      <c r="B90" s="5" t="inlineStr">
+        <is>
+          <t>17/06/2026</t>
+        </is>
+      </c>
+      <c r="C90" s="5" t="inlineStr">
+        <is>
+          <t>Perveen Kousar</t>
+        </is>
+      </c>
+      <c r="D90" s="5" t="inlineStr">
+        <is>
+          <t>71y</t>
+        </is>
+      </c>
+      <c r="E90" s="5" t="inlineStr">
+        <is>
+          <t>Healthcard</t>
+        </is>
+      </c>
+      <c r="G90" s="5" t="inlineStr">
+        <is>
+          <t>Dr. Mukarram Batti</t>
+        </is>
+      </c>
+      <c r="H90" s="5" t="inlineStr">
+        <is>
+          <t>C/Angio + PCI</t>
+        </is>
+      </c>
+      <c r="I90" s="5" t="n">
+        <v>194718</v>
+      </c>
+      <c r="J90" s="5" t="n">
+        <v>11650</v>
+      </c>
+      <c r="K90" s="5" t="n">
+        <v>183068</v>
+      </c>
+      <c r="N90" s="5" t="inlineStr">
+        <is>
+          <t>107250</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="5" t="n">
+        <v>86</v>
+      </c>
+      <c r="B91" s="5" t="inlineStr">
+        <is>
+          <t>17/06/2026</t>
+        </is>
+      </c>
+      <c r="C91" s="5" t="inlineStr">
+        <is>
+          <t>Liaqat</t>
+        </is>
+      </c>
+      <c r="D91" s="5" t="inlineStr">
+        <is>
+          <t>62y</t>
+        </is>
+      </c>
+      <c r="E91" s="5" t="inlineStr">
+        <is>
+          <t>Healthcard</t>
+        </is>
+      </c>
+      <c r="G91" s="5" t="inlineStr">
+        <is>
+          <t>Dr. Anjum Rana</t>
+        </is>
+      </c>
+      <c r="H91" s="5" t="inlineStr">
+        <is>
+          <t>C/Angio + PCI</t>
+        </is>
+      </c>
+      <c r="I91" s="5" t="n">
+        <v>194718</v>
+      </c>
+      <c r="J91" s="5" t="n">
+        <v>11650</v>
+      </c>
+      <c r="K91" s="5" t="n">
+        <v>183068</v>
+      </c>
+      <c r="N91" s="5" t="inlineStr">
+        <is>
+          <t>78500</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="5" t="n">
+        <v>87</v>
+      </c>
+      <c r="B92" s="5" t="inlineStr">
+        <is>
+          <t>17/06/2026</t>
+        </is>
+      </c>
+      <c r="C92" s="5" t="inlineStr">
+        <is>
+          <t>Kiran Shahzadi</t>
+        </is>
+      </c>
+      <c r="D92" s="5" t="inlineStr">
+        <is>
+          <t>35y</t>
+        </is>
+      </c>
+      <c r="E92" s="5" t="inlineStr">
+        <is>
+          <t>Healthcard</t>
+        </is>
+      </c>
+      <c r="G92" s="5" t="inlineStr">
+        <is>
+          <t>Dr. Anjum Rana</t>
+        </is>
+      </c>
+      <c r="H92" s="5" t="inlineStr">
+        <is>
+          <t>C/Angio + PCI</t>
+        </is>
+      </c>
+      <c r="I92" s="5" t="n">
+        <v>194718</v>
+      </c>
+      <c r="J92" s="5" t="n">
+        <v>11650</v>
+      </c>
+      <c r="K92" s="5" t="n">
+        <v>183068</v>
+      </c>
+      <c r="N92" s="5" t="inlineStr">
+        <is>
+          <t>101000</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="5" t="n">
+        <v>88</v>
+      </c>
+      <c r="B93" s="5" t="inlineStr">
+        <is>
+          <t>18/06/2026</t>
+        </is>
+      </c>
+      <c r="C93" s="5" t="inlineStr">
+        <is>
+          <t>M. Irshad</t>
+        </is>
+      </c>
+      <c r="D93" s="5" t="inlineStr">
+        <is>
+          <t>64y</t>
+        </is>
+      </c>
+      <c r="E93" s="5" t="inlineStr">
+        <is>
+          <t>Healthcard</t>
+        </is>
+      </c>
+      <c r="G93" s="5" t="inlineStr">
+        <is>
+          <t>Dr. Arshad Hameed</t>
+        </is>
+      </c>
+      <c r="H93" s="5" t="inlineStr">
+        <is>
+          <t>C/Angio</t>
+        </is>
+      </c>
+      <c r="I93" s="5" t="n">
+        <v>22908</v>
+      </c>
+      <c r="J93" s="5" t="n">
+        <v>1369</v>
+      </c>
+      <c r="K93" s="5" t="n">
+        <v>21539</v>
+      </c>
+      <c r="N93" s="5" t="inlineStr">
+        <is>
+          <t>11500</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="5" t="n">
+        <v>89</v>
+      </c>
+      <c r="B94" s="5" t="inlineStr">
+        <is>
+          <t>18/06/2026</t>
+        </is>
+      </c>
+      <c r="C94" s="5" t="inlineStr">
+        <is>
+          <t>Riffat Naeem</t>
+        </is>
+      </c>
+      <c r="D94" s="5" t="inlineStr">
+        <is>
+          <t>45y</t>
+        </is>
+      </c>
+      <c r="E94" s="5" t="inlineStr">
+        <is>
+          <t>Healthcard</t>
+        </is>
+      </c>
+      <c r="G94" s="5" t="inlineStr">
+        <is>
+          <t>Dr. Anjum Rana</t>
+        </is>
+      </c>
+      <c r="H94" s="5" t="inlineStr">
+        <is>
+          <t>C/Angio + PCI</t>
+        </is>
+      </c>
+      <c r="I94" s="5" t="n">
+        <v>700000</v>
+      </c>
+      <c r="J94" s="5" t="n">
+        <v>17519</v>
+      </c>
+      <c r="K94" s="5" t="n">
+        <v>682481</v>
+      </c>
+      <c r="N94" s="5" t="inlineStr">
+        <is>
+          <t>177000</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="5" t="n">
+        <v>90</v>
+      </c>
+      <c r="B95" s="5" t="inlineStr">
+        <is>
+          <t>18/06/2026</t>
+        </is>
+      </c>
+      <c r="C95" s="5" t="inlineStr">
+        <is>
+          <t>Rasheed</t>
+        </is>
+      </c>
+      <c r="D95" s="5" t="inlineStr">
+        <is>
+          <t>47y</t>
+        </is>
+      </c>
+      <c r="E95" s="5" t="inlineStr">
+        <is>
+          <t>Healthcard</t>
+        </is>
+      </c>
+      <c r="G95" s="5" t="inlineStr">
+        <is>
+          <t>Dr. Arshad</t>
+        </is>
+      </c>
+      <c r="H95" s="5" t="inlineStr">
+        <is>
+          <t>C/Angio + PCI</t>
+        </is>
+      </c>
+      <c r="I95" s="5" t="n">
+        <v>194718</v>
+      </c>
+      <c r="J95" s="5" t="n">
+        <v>11650</v>
+      </c>
+      <c r="K95" s="5" t="n">
+        <v>183068</v>
+      </c>
+      <c r="N95" s="5" t="inlineStr">
+        <is>
+          <t>78500</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="5" t="n">
+        <v>91</v>
+      </c>
+      <c r="B96" s="5" t="inlineStr">
+        <is>
+          <t>18/06/2026</t>
+        </is>
+      </c>
+      <c r="C96" s="5" t="inlineStr">
+        <is>
+          <t>Haneef Bilal</t>
+        </is>
+      </c>
+      <c r="D96" s="5" t="inlineStr">
+        <is>
+          <t>56y</t>
+        </is>
+      </c>
+      <c r="E96" s="5" t="inlineStr">
+        <is>
+          <t>Healthcard</t>
+        </is>
+      </c>
+      <c r="G96" s="5" t="inlineStr">
+        <is>
+          <t>Dr. Suleman Khan</t>
+        </is>
+      </c>
+      <c r="H96" s="5" t="inlineStr">
+        <is>
+          <t>C/Angio + PCI</t>
+        </is>
+      </c>
+      <c r="I96" s="5" t="n">
+        <v>194718</v>
+      </c>
+      <c r="J96" s="5" t="n">
+        <v>11650</v>
+      </c>
+      <c r="K96" s="5" t="n">
+        <v>183068</v>
+      </c>
+      <c r="N96" s="5" t="inlineStr">
+        <is>
+          <t>82500</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="5" t="n">
+        <v>92</v>
+      </c>
+      <c r="B97" s="5" t="inlineStr">
+        <is>
+          <t>19/06/2026</t>
+        </is>
+      </c>
+      <c r="C97" s="5" t="inlineStr">
+        <is>
+          <t>M. Saleem</t>
+        </is>
+      </c>
+      <c r="D97" s="5" t="inlineStr">
+        <is>
+          <t>50y</t>
+        </is>
+      </c>
+      <c r="E97" s="5" t="inlineStr">
+        <is>
+          <t>Healthcard</t>
+        </is>
+      </c>
+      <c r="G97" s="5" t="inlineStr">
+        <is>
+          <t>Dr. Kashif Zaffar</t>
+        </is>
+      </c>
+      <c r="H97" s="5" t="inlineStr">
+        <is>
+          <t>C/Angio</t>
+        </is>
+      </c>
+      <c r="I97" s="5" t="n">
+        <v>22908</v>
+      </c>
+      <c r="J97" s="5" t="n">
+        <v>1369</v>
+      </c>
+      <c r="K97" s="5" t="n">
+        <v>21539</v>
+      </c>
+      <c r="N97" s="5" t="inlineStr">
+        <is>
+          <t>11750</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="5" t="n">
+        <v>93</v>
+      </c>
+      <c r="B98" s="5" t="inlineStr">
+        <is>
+          <t>19/06/2026</t>
+        </is>
+      </c>
+      <c r="C98" s="5" t="inlineStr">
+        <is>
+          <t>Bakht Bibi</t>
+        </is>
+      </c>
+      <c r="D98" s="5" t="inlineStr">
+        <is>
+          <t>66y</t>
+        </is>
+      </c>
+      <c r="E98" s="5" t="inlineStr">
+        <is>
+          <t>Healthcard</t>
+        </is>
+      </c>
+      <c r="G98" s="5" t="inlineStr">
+        <is>
+          <t>Dr. Anjum Rana</t>
+        </is>
+      </c>
+      <c r="H98" s="5" t="inlineStr">
+        <is>
+          <t>C/Angio</t>
+        </is>
+      </c>
+      <c r="I98" s="5" t="n">
+        <v>22908</v>
+      </c>
+      <c r="J98" s="5" t="n">
+        <v>1369</v>
+      </c>
+      <c r="K98" s="5" t="n">
+        <v>21539</v>
+      </c>
+      <c r="N98" s="5" t="inlineStr">
+        <is>
+          <t>11500</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="5" t="n">
+        <v>94</v>
+      </c>
+      <c r="B99" s="5" t="inlineStr">
+        <is>
+          <t>19/06/2026</t>
+        </is>
+      </c>
+      <c r="C99" s="5" t="inlineStr">
+        <is>
+          <t>Fiaz Rasool</t>
+        </is>
+      </c>
+      <c r="D99" s="5" t="inlineStr">
+        <is>
+          <t>50y</t>
+        </is>
+      </c>
+      <c r="E99" s="5" t="inlineStr">
+        <is>
+          <t>Healthcard</t>
+        </is>
+      </c>
+      <c r="G99" s="5" t="inlineStr">
+        <is>
+          <t>Dr. Suleman Khan</t>
+        </is>
+      </c>
+      <c r="H99" s="5" t="inlineStr">
+        <is>
+          <t>C/Angio</t>
+        </is>
+      </c>
+      <c r="I99" s="5" t="n">
+        <v>22908</v>
+      </c>
+      <c r="J99" s="5" t="n">
+        <v>1369</v>
+      </c>
+      <c r="K99" s="5" t="n">
+        <v>21539</v>
+      </c>
+      <c r="N99" s="5" t="inlineStr">
+        <is>
+          <t>11500</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="5" t="n">
+        <v>95</v>
+      </c>
+      <c r="B100" s="5" t="inlineStr">
+        <is>
+          <t>19/06/2026</t>
+        </is>
+      </c>
+      <c r="C100" s="5" t="inlineStr">
+        <is>
+          <t>Sayyan</t>
+        </is>
+      </c>
+      <c r="D100" s="5" t="inlineStr">
+        <is>
+          <t>53y</t>
+        </is>
+      </c>
+      <c r="E100" s="5" t="inlineStr">
+        <is>
+          <t>Healthcard</t>
+        </is>
+      </c>
+      <c r="G100" s="5" t="inlineStr">
+        <is>
+          <t>Dr. Suleman Khan</t>
+        </is>
+      </c>
+      <c r="H100" s="5" t="inlineStr">
+        <is>
+          <t>C/Angio</t>
+        </is>
+      </c>
+      <c r="I100" s="5" t="n">
+        <v>22908</v>
+      </c>
+      <c r="J100" s="5" t="n">
+        <v>1369</v>
+      </c>
+      <c r="K100" s="5" t="n">
+        <v>21539</v>
+      </c>
+      <c r="N100" s="5" t="inlineStr">
+        <is>
+          <t>11500</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="5" t="n">
+        <v>96</v>
+      </c>
+      <c r="B101" s="5" t="inlineStr">
+        <is>
+          <t>19/06/2026</t>
+        </is>
+      </c>
+      <c r="C101" s="5" t="inlineStr">
+        <is>
+          <t>Bushra Bibi</t>
+        </is>
+      </c>
+      <c r="D101" s="5" t="inlineStr">
+        <is>
+          <t>68y</t>
+        </is>
+      </c>
+      <c r="E101" s="5" t="inlineStr">
+        <is>
+          <t>Healthcard</t>
+        </is>
+      </c>
+      <c r="G101" s="5" t="inlineStr">
+        <is>
+          <t>Dr. Matti-ullah</t>
+        </is>
+      </c>
+      <c r="H101" s="5" t="inlineStr">
+        <is>
+          <t>C/Angio</t>
+        </is>
+      </c>
+      <c r="I101" s="5" t="n">
+        <v>22908</v>
+      </c>
+      <c r="J101" s="5" t="n">
+        <v>1369</v>
+      </c>
+      <c r="K101" s="5" t="n">
+        <v>21539</v>
+      </c>
+      <c r="N101" s="5" t="inlineStr">
+        <is>
+          <t>13500</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="5" t="n">
+        <v>97</v>
+      </c>
+      <c r="B102" s="5" t="inlineStr">
+        <is>
+          <t>19/06/2026</t>
+        </is>
+      </c>
+      <c r="C102" s="5" t="inlineStr">
+        <is>
+          <t>Naeem Gulzar</t>
+        </is>
+      </c>
+      <c r="D102" s="5" t="inlineStr">
+        <is>
+          <t>58y</t>
+        </is>
+      </c>
+      <c r="E102" s="5" t="inlineStr">
+        <is>
+          <t>Healthcard</t>
+        </is>
+      </c>
+      <c r="G102" s="5" t="inlineStr">
+        <is>
+          <t>Dr. Kashif Zaffar</t>
+        </is>
+      </c>
+      <c r="H102" s="5" t="inlineStr">
+        <is>
+          <t>C/Angio</t>
+        </is>
+      </c>
+      <c r="I102" s="5" t="n">
+        <v>22908</v>
+      </c>
+      <c r="J102" s="5" t="n">
+        <v>1369</v>
+      </c>
+      <c r="K102" s="5" t="n">
+        <v>21539</v>
+      </c>
+      <c r="N102" s="5" t="inlineStr">
+        <is>
+          <t>11750</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="5" t="n">
+        <v>98</v>
+      </c>
+      <c r="B103" s="5" t="inlineStr">
+        <is>
+          <t>19/06/2026</t>
+        </is>
+      </c>
+      <c r="C103" s="5" t="inlineStr">
+        <is>
+          <t>M. Fiaz</t>
+        </is>
+      </c>
+      <c r="D103" s="5" t="inlineStr">
+        <is>
+          <t>65y</t>
+        </is>
+      </c>
+      <c r="E103" s="5" t="inlineStr">
+        <is>
+          <t>Healthcard</t>
+        </is>
+      </c>
+      <c r="G103" s="5" t="inlineStr">
+        <is>
+          <t>Dr. Suleman Khan</t>
+        </is>
+      </c>
+      <c r="H103" s="5" t="inlineStr">
+        <is>
+          <t>C/Angio + PCI</t>
+        </is>
+      </c>
+      <c r="I103" s="5" t="n">
+        <v>343620</v>
+      </c>
+      <c r="J103" s="5" t="n">
+        <v>20542</v>
+      </c>
+      <c r="K103" s="5" t="n">
+        <v>323078</v>
+      </c>
+      <c r="N103" s="5" t="inlineStr">
+        <is>
+          <t>205880</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="5" t="n">
+        <v>99</v>
+      </c>
+      <c r="B104" s="5" t="inlineStr">
+        <is>
+          <t>19/06/2026</t>
+        </is>
+      </c>
+      <c r="C104" s="5" t="inlineStr">
+        <is>
+          <t>Zahid</t>
+        </is>
+      </c>
+      <c r="D104" s="5" t="inlineStr">
+        <is>
+          <t>47y</t>
+        </is>
+      </c>
+      <c r="E104" s="5" t="inlineStr">
+        <is>
+          <t>Healthcard</t>
+        </is>
+      </c>
+      <c r="G104" s="5" t="inlineStr">
+        <is>
+          <t>Dr. Suleman Khan</t>
+        </is>
+      </c>
+      <c r="H104" s="5" t="inlineStr">
+        <is>
+          <t>C/Angio + PCI</t>
+        </is>
+      </c>
+      <c r="I104" s="5" t="n">
+        <v>194718</v>
+      </c>
+      <c r="J104" s="5" t="n">
+        <v>11650</v>
+      </c>
+      <c r="K104" s="5" t="n">
+        <v>183068</v>
+      </c>
+      <c r="N104" s="5" t="inlineStr">
+        <is>
+          <t>80000</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="5" t="n">
+        <v>100</v>
+      </c>
+      <c r="B105" s="5" t="inlineStr">
+        <is>
+          <t>19/06/2026</t>
+        </is>
+      </c>
+      <c r="C105" s="5" t="inlineStr">
+        <is>
+          <t>Ghulam Bibi</t>
+        </is>
+      </c>
+      <c r="D105" s="5" t="inlineStr">
+        <is>
+          <t>67y</t>
+        </is>
+      </c>
+      <c r="E105" s="5" t="inlineStr">
+        <is>
+          <t>Healthcard</t>
+        </is>
+      </c>
+      <c r="G105" s="5" t="inlineStr">
+        <is>
+          <t>Dr. Anjum Rana</t>
+        </is>
+      </c>
+      <c r="H105" s="5" t="inlineStr">
+        <is>
+          <t>C/Angio + PCI</t>
+        </is>
+      </c>
+      <c r="I105" s="5" t="n">
+        <v>194718</v>
+      </c>
+      <c r="J105" s="5" t="n">
+        <v>11650</v>
+      </c>
+      <c r="K105" s="5" t="n">
+        <v>183068</v>
+      </c>
+      <c r="N105" s="5" t="inlineStr">
+        <is>
+          <t>99000</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="5" t="n">
+        <v>101</v>
+      </c>
+      <c r="B106" s="5" t="inlineStr">
+        <is>
+          <t>20/06/2026</t>
+        </is>
+      </c>
+      <c r="C106" s="5" t="inlineStr">
+        <is>
+          <t>Abdul Islam</t>
+        </is>
+      </c>
+      <c r="D106" s="5" t="inlineStr">
+        <is>
+          <t>54y</t>
+        </is>
+      </c>
+      <c r="E106" s="5" t="inlineStr">
+        <is>
+          <t>Healthcard</t>
+        </is>
+      </c>
+      <c r="G106" s="5" t="inlineStr">
+        <is>
+          <t>Dr. Anjum Rana</t>
+        </is>
+      </c>
+      <c r="H106" s="5" t="inlineStr">
+        <is>
+          <t>C/Angio</t>
+        </is>
+      </c>
+      <c r="I106" s="5" t="n">
+        <v>22908</v>
+      </c>
+      <c r="J106" s="5" t="n">
+        <v>1369</v>
+      </c>
+      <c r="K106" s="5" t="n">
+        <v>21539</v>
+      </c>
+      <c r="N106" s="5" t="inlineStr">
+        <is>
+          <t>11500</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="5" t="n">
+        <v>102</v>
+      </c>
+      <c r="B107" s="5" t="inlineStr">
+        <is>
+          <t>20/06/2026</t>
+        </is>
+      </c>
+      <c r="C107" s="5" t="inlineStr">
+        <is>
+          <t>Anwar Hussain</t>
+        </is>
+      </c>
+      <c r="D107" s="5" t="inlineStr">
+        <is>
+          <t>50y</t>
+        </is>
+      </c>
+      <c r="E107" s="5" t="inlineStr">
+        <is>
+          <t>Healthcard</t>
+        </is>
+      </c>
+      <c r="G107" s="5" t="inlineStr">
+        <is>
+          <t>Dr. Anjum Rana</t>
+        </is>
+      </c>
+      <c r="H107" s="5" t="inlineStr">
+        <is>
+          <t>C/Angio + PCI</t>
+        </is>
+      </c>
+      <c r="I107" s="5" t="n">
+        <v>286350</v>
+      </c>
+      <c r="J107" s="5" t="n">
+        <v>17519</v>
+      </c>
+      <c r="K107" s="5" t="n">
+        <v>268831</v>
+      </c>
+      <c r="N107" s="5" t="inlineStr">
+        <is>
+          <t>128500</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="5" t="n">
+        <v>103</v>
+      </c>
+      <c r="B108" s="5" t="inlineStr">
+        <is>
+          <t>20/06/2026</t>
+        </is>
+      </c>
+      <c r="C108" s="5" t="inlineStr">
+        <is>
+          <t>Asif</t>
+        </is>
+      </c>
+      <c r="D108" s="5" t="inlineStr">
+        <is>
+          <t>50y</t>
+        </is>
+      </c>
+      <c r="E108" s="5" t="inlineStr">
+        <is>
+          <t>Healthcard</t>
+        </is>
+      </c>
+      <c r="G108" s="5" t="inlineStr">
+        <is>
+          <t>Dr. Anjum Rana</t>
+        </is>
+      </c>
+      <c r="H108" s="5" t="inlineStr">
+        <is>
+          <t>C/Angio + PCI</t>
+        </is>
+      </c>
+      <c r="I108" s="5" t="n">
+        <v>194718</v>
+      </c>
+      <c r="J108" s="5" t="n">
+        <v>11650</v>
+      </c>
+      <c r="K108" s="5" t="n">
+        <v>183068</v>
+      </c>
+      <c r="N108" s="5" t="inlineStr">
+        <is>
+          <t>91000</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="5" t="n">
+        <v>104</v>
+      </c>
+      <c r="B109" s="5" t="inlineStr">
+        <is>
+          <t>22/06/2026</t>
+        </is>
+      </c>
+      <c r="C109" s="5" t="inlineStr">
+        <is>
+          <t>M. Aleem</t>
+        </is>
+      </c>
+      <c r="D109" s="5" t="inlineStr">
+        <is>
+          <t>50y</t>
+        </is>
+      </c>
+      <c r="E109" s="5" t="inlineStr">
+        <is>
+          <t>Healthcard</t>
+        </is>
+      </c>
+      <c r="G109" s="5" t="inlineStr">
+        <is>
+          <t>Dr. Anjum Rana</t>
+        </is>
+      </c>
+      <c r="H109" s="5" t="inlineStr">
+        <is>
+          <t>C/Angio</t>
+        </is>
+      </c>
+      <c r="I109" s="5" t="n">
+        <v>22908</v>
+      </c>
+      <c r="J109" s="5" t="n">
+        <v>1369</v>
+      </c>
+      <c r="K109" s="5" t="n">
+        <v>21539</v>
+      </c>
+      <c r="N109" s="5" t="inlineStr">
+        <is>
+          <t>11500</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="5" t="n">
+        <v>105</v>
+      </c>
+      <c r="B110" s="5" t="inlineStr">
+        <is>
+          <t>22/06/2026</t>
+        </is>
+      </c>
+      <c r="C110" s="5" t="inlineStr">
+        <is>
+          <t>M. Mansha</t>
+        </is>
+      </c>
+      <c r="D110" s="5" t="inlineStr">
+        <is>
+          <t>55y</t>
+        </is>
+      </c>
+      <c r="E110" s="5" t="inlineStr">
+        <is>
+          <t>Healthcard</t>
+        </is>
+      </c>
+      <c r="G110" s="5" t="inlineStr">
+        <is>
+          <t>Dr. Suleman Khan</t>
+        </is>
+      </c>
+      <c r="H110" s="5" t="inlineStr">
+        <is>
+          <t>C/Angio</t>
+        </is>
+      </c>
+      <c r="I110" s="5" t="n">
+        <v>22908</v>
+      </c>
+      <c r="J110" s="5" t="n">
+        <v>1369</v>
+      </c>
+      <c r="K110" s="5" t="n">
+        <v>21539</v>
+      </c>
+      <c r="N110" s="5" t="inlineStr">
+        <is>
+          <t>9000</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="5" t="n">
+        <v>106</v>
+      </c>
+      <c r="B111" s="5" t="inlineStr">
+        <is>
+          <t>22/06/2026</t>
+        </is>
+      </c>
+      <c r="C111" s="5" t="inlineStr">
+        <is>
+          <t>Rasheed Ahmad</t>
+        </is>
+      </c>
+      <c r="D111" s="5" t="inlineStr">
+        <is>
+          <t>46y</t>
+        </is>
+      </c>
+      <c r="E111" s="5" t="inlineStr">
+        <is>
+          <t>Healthcard</t>
+        </is>
+      </c>
+      <c r="G111" s="5" t="inlineStr">
+        <is>
+          <t>Dr. Suleman Khan</t>
+        </is>
+      </c>
+      <c r="H111" s="5" t="inlineStr">
+        <is>
+          <t>C/Angio</t>
+        </is>
+      </c>
+      <c r="I111" s="5" t="n">
+        <v>22908</v>
+      </c>
+      <c r="J111" s="5" t="n">
+        <v>1369</v>
+      </c>
+      <c r="K111" s="5" t="n">
+        <v>21539</v>
+      </c>
+      <c r="N111" s="5" t="inlineStr">
+        <is>
+          <t>11500</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="5" t="n">
+        <v>107</v>
+      </c>
+      <c r="B112" s="5" t="inlineStr">
+        <is>
+          <t>22/06/2026</t>
+        </is>
+      </c>
+      <c r="C112" s="5" t="inlineStr">
+        <is>
+          <t>Kousar</t>
+        </is>
+      </c>
+      <c r="D112" s="5" t="inlineStr">
+        <is>
+          <t>98y</t>
+        </is>
+      </c>
+      <c r="E112" s="5" t="inlineStr">
+        <is>
+          <t>Healthcard</t>
+        </is>
+      </c>
+      <c r="G112" s="5" t="inlineStr">
+        <is>
+          <t>Dr. Anjum Rana</t>
+        </is>
+      </c>
+      <c r="H112" s="5" t="inlineStr">
+        <is>
+          <t>C/Angio</t>
+        </is>
+      </c>
+      <c r="I112" s="5" t="n">
+        <v>22908</v>
+      </c>
+      <c r="J112" s="5" t="n">
+        <v>1369</v>
+      </c>
+      <c r="K112" s="5" t="n">
+        <v>21539</v>
+      </c>
+      <c r="N112" s="5" t="inlineStr">
+        <is>
+          <t>11500</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="5" t="n">
+        <v>108</v>
+      </c>
+      <c r="B113" s="5" t="inlineStr">
+        <is>
+          <t>22/06/2026</t>
+        </is>
+      </c>
+      <c r="C113" s="5" t="inlineStr">
+        <is>
+          <t>Said Muhammad</t>
+        </is>
+      </c>
+      <c r="D113" s="5" t="inlineStr">
+        <is>
+          <t>68y</t>
+        </is>
+      </c>
+      <c r="E113" s="5" t="inlineStr">
+        <is>
+          <t>Healthcard</t>
+        </is>
+      </c>
+      <c r="G113" s="5" t="inlineStr">
+        <is>
+          <t>Dr. M. Ijaz</t>
+        </is>
+      </c>
+      <c r="H113" s="5" t="inlineStr">
+        <is>
+          <t>C/Angio + PCI</t>
+        </is>
+      </c>
+      <c r="I113" s="5" t="n">
+        <v>286350</v>
+      </c>
+      <c r="J113" s="5" t="n">
+        <v>17519</v>
+      </c>
+      <c r="K113" s="5" t="n">
+        <v>268831</v>
+      </c>
+      <c r="N113" s="5" t="inlineStr">
+        <is>
+          <t>167500</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="5" t="n">
+        <v>109</v>
+      </c>
+      <c r="B114" s="5" t="inlineStr">
+        <is>
+          <t>22/06/2026</t>
+        </is>
+      </c>
+      <c r="C114" s="5" t="inlineStr">
+        <is>
+          <t>Hafiz Naeeem</t>
+        </is>
+      </c>
+      <c r="D114" s="5" t="inlineStr">
+        <is>
+          <t>53y</t>
+        </is>
+      </c>
+      <c r="E114" s="5" t="inlineStr">
+        <is>
+          <t>Healthcard</t>
+        </is>
+      </c>
+      <c r="G114" s="5" t="inlineStr">
+        <is>
+          <t>Dr. Anjum Rana</t>
+        </is>
+      </c>
+      <c r="H114" s="5" t="inlineStr">
+        <is>
+          <t>C/Angio + PCI</t>
+        </is>
+      </c>
+      <c r="I114" s="5" t="n">
+        <v>350000</v>
+      </c>
+      <c r="J114" s="5" t="n">
+        <v>11650</v>
+      </c>
+      <c r="K114" s="5" t="n">
+        <v>338350</v>
+      </c>
+      <c r="N114" s="5" t="inlineStr">
+        <is>
+          <t>102000</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="5" t="n">
+        <v>110</v>
+      </c>
+      <c r="B115" s="5" t="inlineStr">
+        <is>
+          <t>22/06/2026</t>
+        </is>
+      </c>
+      <c r="C115" s="5" t="inlineStr">
+        <is>
+          <t>M. Saleem</t>
+        </is>
+      </c>
+      <c r="D115" s="5" t="inlineStr">
+        <is>
+          <t>55y</t>
+        </is>
+      </c>
+      <c r="E115" s="5" t="inlineStr">
+        <is>
+          <t>Healthcard</t>
+        </is>
+      </c>
+      <c r="G115" s="5" t="inlineStr">
+        <is>
+          <t>Dr. Kashif Zaffar</t>
+        </is>
+      </c>
+      <c r="H115" s="5" t="inlineStr">
+        <is>
+          <t>C/Angio + PCI</t>
+        </is>
+      </c>
+      <c r="I115" s="5" t="n">
+        <v>194718</v>
+      </c>
+      <c r="J115" s="5" t="n">
+        <v>17519</v>
+      </c>
+      <c r="K115" s="5" t="n">
+        <v>177199</v>
+      </c>
+      <c r="N115" s="5" t="inlineStr">
+        <is>
+          <t>107250</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="5" t="n">
+        <v>111</v>
+      </c>
+      <c r="B116" s="5" t="inlineStr">
+        <is>
+          <t>23/06/2026</t>
+        </is>
+      </c>
+      <c r="C116" s="5" t="inlineStr">
+        <is>
+          <t>M. Iqbal</t>
+        </is>
+      </c>
+      <c r="D116" s="5" t="inlineStr">
+        <is>
+          <t>50y</t>
+        </is>
+      </c>
+      <c r="E116" s="5" t="inlineStr">
+        <is>
+          <t>Healthcard</t>
+        </is>
+      </c>
+      <c r="G116" s="5" t="inlineStr">
+        <is>
+          <t>Dr. Anjum Rana</t>
+        </is>
+      </c>
+      <c r="H116" s="5" t="inlineStr">
+        <is>
+          <t>C/Angio</t>
+        </is>
+      </c>
+      <c r="I116" s="5" t="n">
+        <v>22908</v>
+      </c>
+      <c r="J116" s="5" t="n">
+        <v>1369</v>
+      </c>
+      <c r="K116" s="5" t="n">
+        <v>21539</v>
+      </c>
+      <c r="N116" s="5" t="inlineStr">
+        <is>
+          <t>11500</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="5" t="n">
+        <v>112</v>
+      </c>
+      <c r="B117" s="5" t="inlineStr">
+        <is>
+          <t>23/06/2026</t>
+        </is>
+      </c>
+      <c r="C117" s="5" t="inlineStr">
+        <is>
+          <t>Ghulam Kubra</t>
+        </is>
+      </c>
+      <c r="D117" s="5" t="inlineStr">
+        <is>
+          <t>66y</t>
+        </is>
+      </c>
+      <c r="E117" s="5" t="inlineStr">
+        <is>
+          <t>Healthcard</t>
+        </is>
+      </c>
+      <c r="G117" s="5" t="inlineStr">
+        <is>
+          <t>Dr. Anjum Rana</t>
+        </is>
+      </c>
+      <c r="H117" s="5" t="inlineStr">
+        <is>
+          <t>C/Angio</t>
+        </is>
+      </c>
+      <c r="I117" s="5" t="n">
+        <v>35000</v>
+      </c>
+      <c r="J117" s="5" t="n">
+        <v>1369</v>
+      </c>
+      <c r="K117" s="5" t="n">
+        <v>33631</v>
+      </c>
+      <c r="N117" s="5" t="inlineStr">
+        <is>
+          <t>11500</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="5" t="n">
+        <v>113</v>
+      </c>
+      <c r="B118" s="5" t="inlineStr">
+        <is>
+          <t>23/06/2026</t>
+        </is>
+      </c>
+      <c r="C118" s="5" t="inlineStr">
+        <is>
+          <t>M. Mansha</t>
+        </is>
+      </c>
+      <c r="D118" s="5" t="inlineStr">
+        <is>
+          <t>55y</t>
+        </is>
+      </c>
+      <c r="E118" s="5" t="inlineStr">
+        <is>
+          <t>Healthcard</t>
+        </is>
+      </c>
+      <c r="G118" s="5" t="inlineStr">
+        <is>
+          <t>Dr. Suleman Khan</t>
+        </is>
+      </c>
+      <c r="H118" s="5" t="inlineStr">
+        <is>
+          <t>C/Angio + PCI</t>
+        </is>
+      </c>
+      <c r="I118" s="5" t="n">
+        <v>173804</v>
+      </c>
+      <c r="J118" s="5" t="n">
+        <v>11650</v>
+      </c>
+      <c r="K118" s="5" t="n">
+        <v>162154</v>
+      </c>
+      <c r="N118" s="5" t="inlineStr">
+        <is>
+          <t>75500</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="5" t="n">
+        <v>114</v>
+      </c>
+      <c r="B119" s="5" t="inlineStr">
+        <is>
+          <t>23/06/2026</t>
+        </is>
+      </c>
+      <c r="C119" s="5" t="inlineStr">
+        <is>
+          <t>Samina Kousar</t>
+        </is>
+      </c>
+      <c r="D119" s="5" t="inlineStr">
+        <is>
+          <t>73y</t>
+        </is>
+      </c>
+      <c r="E119" s="5" t="inlineStr">
+        <is>
+          <t>Healthcard</t>
+        </is>
+      </c>
+      <c r="G119" s="5" t="inlineStr">
+        <is>
+          <t>Dr. Suleman Khan</t>
+        </is>
+      </c>
+      <c r="H119" s="5" t="inlineStr">
+        <is>
+          <t>C/Angio + PCI</t>
+        </is>
+      </c>
+      <c r="I119" s="5" t="n">
+        <v>194718</v>
+      </c>
+      <c r="J119" s="5" t="n">
+        <v>11650</v>
+      </c>
+      <c r="K119" s="5" t="n">
+        <v>183068</v>
+      </c>
+      <c r="N119" s="5" t="inlineStr">
+        <is>
+          <t>89000</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="5" t="n">
+        <v>115</v>
+      </c>
+      <c r="B120" s="5" t="inlineStr">
+        <is>
+          <t>23/06/2026</t>
+        </is>
+      </c>
+      <c r="C120" s="5" t="inlineStr">
+        <is>
+          <t>Shamshad Bibi</t>
+        </is>
+      </c>
+      <c r="D120" s="5" t="inlineStr">
+        <is>
+          <t>50y</t>
+        </is>
+      </c>
+      <c r="E120" s="5" t="inlineStr">
+        <is>
+          <t>Healthcard</t>
+        </is>
+      </c>
+      <c r="G120" s="5" t="inlineStr">
+        <is>
+          <t>Dr. Anjum Rana</t>
+        </is>
+      </c>
+      <c r="H120" s="5" t="inlineStr">
+        <is>
+          <t>C/Angio + PCI</t>
+        </is>
+      </c>
+      <c r="I120" s="5" t="n">
+        <v>283650</v>
+      </c>
+      <c r="J120" s="5" t="n">
+        <v>17519</v>
+      </c>
+      <c r="K120" s="5" t="n">
+        <v>266131</v>
+      </c>
+      <c r="N120" s="5" t="inlineStr">
+        <is>
+          <t>139000</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="5" t="n">
+        <v>116</v>
+      </c>
+      <c r="B121" s="5" t="inlineStr">
+        <is>
+          <t>23/06/2026</t>
+        </is>
+      </c>
+      <c r="C121" s="5" t="inlineStr">
+        <is>
+          <t>Shabi</t>
+        </is>
+      </c>
+      <c r="D121" s="5" t="inlineStr">
+        <is>
+          <t>43y</t>
+        </is>
+      </c>
+      <c r="E121" s="5" t="inlineStr">
+        <is>
+          <t>Healthcard</t>
+        </is>
+      </c>
+      <c r="G121" s="5" t="inlineStr">
+        <is>
+          <t>Dr. Suleman Khan</t>
+        </is>
+      </c>
+      <c r="H121" s="5" t="inlineStr">
+        <is>
+          <t>C/Angio + PCI + Plasty</t>
+        </is>
+      </c>
+      <c r="I121" s="5" t="n">
+        <v>1000000</v>
+      </c>
+      <c r="J121" s="5" t="n">
+        <v>20542</v>
+      </c>
+      <c r="K121" s="5" t="n">
+        <v>979458</v>
+      </c>
+      <c r="N121" s="5" t="inlineStr">
+        <is>
+          <t>250500</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="5" t="n">
+        <v>117</v>
+      </c>
+      <c r="B122" s="5" t="inlineStr">
+        <is>
+          <t>24/06/2026</t>
+        </is>
+      </c>
+      <c r="C122" s="5" t="inlineStr">
+        <is>
+          <t>Abdul Rouf Ijaz</t>
+        </is>
+      </c>
+      <c r="D122" s="5" t="inlineStr">
+        <is>
+          <t>53y</t>
+        </is>
+      </c>
+      <c r="E122" s="5" t="inlineStr">
+        <is>
+          <t>Healthcard</t>
+        </is>
+      </c>
+      <c r="G122" s="5" t="inlineStr">
+        <is>
+          <t>Dr. Mukarram Batti</t>
+        </is>
+      </c>
+      <c r="H122" s="5" t="inlineStr">
+        <is>
+          <t>C/Angio + PCI</t>
+        </is>
+      </c>
+      <c r="I122" s="5" t="n">
+        <v>194718</v>
+      </c>
+      <c r="J122" s="5" t="n">
+        <v>11650</v>
+      </c>
+      <c r="K122" s="5" t="n">
+        <v>183068</v>
+      </c>
+      <c r="N122" s="5" t="inlineStr">
+        <is>
+          <t>134750</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="5" t="n">
+        <v>118</v>
+      </c>
+      <c r="B123" s="5" t="inlineStr">
+        <is>
+          <t>24/06/2026</t>
+        </is>
+      </c>
+      <c r="C123" s="5" t="inlineStr">
+        <is>
+          <t>Shahid Anjum</t>
+        </is>
+      </c>
+      <c r="D123" s="5" t="inlineStr">
+        <is>
+          <t>50y</t>
+        </is>
+      </c>
+      <c r="E123" s="5" t="inlineStr">
+        <is>
+          <t>Healthcard</t>
+        </is>
+      </c>
+      <c r="G123" s="5" t="inlineStr">
+        <is>
+          <t>Dr. Aqeel Malik</t>
+        </is>
+      </c>
+      <c r="H123" s="5" t="inlineStr">
+        <is>
+          <t>C/Angio + PCI</t>
+        </is>
+      </c>
+      <c r="I123" s="5" t="n">
+        <v>265434</v>
+      </c>
+      <c r="J123" s="5" t="n">
+        <v>17519</v>
+      </c>
+      <c r="K123" s="5" t="n">
+        <v>247915</v>
+      </c>
+      <c r="N123" s="5" t="inlineStr">
+        <is>
+          <t>16500</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="5" t="n">
+        <v>119</v>
+      </c>
+      <c r="B124" s="5" t="inlineStr">
+        <is>
+          <t>27/06/2026</t>
+        </is>
+      </c>
+      <c r="C124" s="5" t="inlineStr">
+        <is>
+          <t>Saifullah</t>
+        </is>
+      </c>
+      <c r="D124" s="5" t="inlineStr">
+        <is>
+          <t>49y</t>
+        </is>
+      </c>
+      <c r="E124" s="5" t="inlineStr">
+        <is>
+          <t>Healthcard</t>
+        </is>
+      </c>
+      <c r="G124" s="5" t="inlineStr">
+        <is>
+          <t>Dr. Suleman Khan</t>
+        </is>
+      </c>
+      <c r="H124" s="5" t="inlineStr">
+        <is>
+          <t>C/Angio</t>
+        </is>
+      </c>
+      <c r="I124" s="5" t="n">
+        <v>22908</v>
+      </c>
+      <c r="J124" s="5" t="n">
+        <v>1369</v>
+      </c>
+      <c r="K124" s="5" t="n">
+        <v>21539</v>
+      </c>
+      <c r="N124" s="5" t="inlineStr">
+        <is>
+          <t>9000</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="5" t="n">
+        <v>120</v>
+      </c>
+      <c r="B125" s="5" t="inlineStr">
+        <is>
+          <t>27/06/2026</t>
+        </is>
+      </c>
+      <c r="C125" s="5" t="inlineStr">
+        <is>
+          <t>Ghulam Sakina</t>
+        </is>
+      </c>
+      <c r="D125" s="5" t="inlineStr">
+        <is>
+          <t>58y</t>
+        </is>
+      </c>
+      <c r="E125" s="5" t="inlineStr">
+        <is>
+          <t>Healthcard</t>
+        </is>
+      </c>
+      <c r="G125" s="5" t="inlineStr">
+        <is>
+          <t>Dr. Suleman Khan</t>
+        </is>
+      </c>
+      <c r="H125" s="5" t="inlineStr">
+        <is>
+          <t>C/Angio + PCI</t>
+        </is>
+      </c>
+      <c r="I125" s="5" t="n">
+        <v>343620</v>
+      </c>
+      <c r="J125" s="5" t="n">
+        <v>20542</v>
+      </c>
+      <c r="K125" s="5" t="n">
+        <v>323078</v>
+      </c>
+      <c r="N125" s="5" t="inlineStr">
+        <is>
+          <t>166500</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="5" t="n">
+        <v>121</v>
+      </c>
+      <c r="B126" s="5" t="inlineStr">
+        <is>
+          <t>27/06/2026</t>
+        </is>
+      </c>
+      <c r="C126" s="5" t="inlineStr">
+        <is>
+          <t>Rasool Bibi</t>
+        </is>
+      </c>
+      <c r="D126" s="5" t="inlineStr">
+        <is>
+          <t>60y</t>
+        </is>
+      </c>
+      <c r="E126" s="5" t="inlineStr">
+        <is>
+          <t>Healthcard</t>
+        </is>
+      </c>
+      <c r="G126" s="5" t="inlineStr">
+        <is>
+          <t>Dr. Zaffar - Ullah</t>
+        </is>
+      </c>
+      <c r="H126" s="5" t="inlineStr">
+        <is>
+          <t>C/Angio + PCI</t>
+        </is>
+      </c>
+      <c r="I126" s="5" t="n">
+        <v>286350</v>
+      </c>
+      <c r="J126" s="5" t="n">
+        <v>20542</v>
+      </c>
+      <c r="K126" s="5" t="n">
+        <v>265808</v>
+      </c>
+      <c r="N126" s="5" t="inlineStr">
+        <is>
+          <t>137500</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="5" t="n">
+        <v>122</v>
+      </c>
+      <c r="B127" s="5" t="inlineStr">
+        <is>
+          <t>27/06/2026</t>
+        </is>
+      </c>
+      <c r="C127" s="5" t="inlineStr">
+        <is>
+          <t>Sadaqat Hussain</t>
+        </is>
+      </c>
+      <c r="D127" s="5" t="inlineStr">
+        <is>
+          <t>45y</t>
+        </is>
+      </c>
+      <c r="E127" s="5" t="inlineStr">
+        <is>
+          <t>Healthcard</t>
+        </is>
+      </c>
+      <c r="G127" s="5" t="inlineStr">
+        <is>
+          <t>Dr. Suleman Khan</t>
+        </is>
+      </c>
+      <c r="H127" s="5" t="inlineStr">
+        <is>
+          <t>C/Angio + PCI</t>
+        </is>
+      </c>
+      <c r="I127" s="5" t="n">
+        <v>286350</v>
+      </c>
+      <c r="J127" s="5" t="n">
+        <v>17519</v>
+      </c>
+      <c r="K127" s="5" t="n">
+        <v>268831</v>
+      </c>
+      <c r="N127" s="5" t="inlineStr">
+        <is>
+          <t>116000</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="5" t="n">
+        <v>123</v>
+      </c>
+      <c r="B128" s="5" t="inlineStr">
+        <is>
+          <t>27/06/2026</t>
+        </is>
+      </c>
+      <c r="C128" s="5" t="inlineStr">
+        <is>
+          <t>Azhar Shahzad</t>
+        </is>
+      </c>
+      <c r="D128" s="5" t="inlineStr">
+        <is>
+          <t>54y</t>
+        </is>
+      </c>
+      <c r="E128" s="5" t="inlineStr">
+        <is>
+          <t>Healthcard</t>
+        </is>
+      </c>
+      <c r="G128" s="5" t="inlineStr">
+        <is>
+          <t>Dr. Zaffar - Ullah</t>
+        </is>
+      </c>
+      <c r="H128" s="5" t="inlineStr">
+        <is>
+          <t>C/Angio + PCI</t>
+        </is>
+      </c>
+      <c r="I128" s="5" t="n">
+        <v>194718</v>
+      </c>
+      <c r="J128" s="5" t="n">
+        <v>11650</v>
+      </c>
+      <c r="K128" s="5" t="n">
+        <v>183068</v>
+      </c>
+      <c r="N128" s="5" t="inlineStr">
+        <is>
+          <t>84500</t>
         </is>
       </c>
     </row>
